--- a/research/traditional_assets/database/data/new_zealand/new_zealand_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_healthcare_products.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09083876366469271</v>
+        <v>0.09061681512643156</v>
       </c>
       <c r="C2">
-        <v>12656.75666641738</v>
+        <v>12592.05488639566</v>
       </c>
       <c r="D2">
-        <v>12582.55666641738</v>
+        <v>12644.86988639566</v>
       </c>
       <c r="E2">
-        <v>-96</v>
+        <v>31.015</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>127.015</v>
       </c>
       <c r="G2">
         <v>74.2</v>
@@ -1576,28 +1576,28 @@
         <v>266.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.3888545</v>
       </c>
       <c r="N2">
-        <v>266.6</v>
+        <v>260.2111455</v>
       </c>
       <c r="O2">
-        <v>74.64800000000001</v>
+        <v>72.85912074000002</v>
       </c>
       <c r="P2">
-        <v>191.952</v>
+        <v>187.35202476</v>
       </c>
       <c r="Q2">
-        <v>257.652</v>
+        <v>253.05202476</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09083876366469271</v>
+        <v>0.09116631830952683</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.047720977125331</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>41.72892026262299</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09061681512643156</v>
+        <v>0.09039486658817042</v>
       </c>
       <c r="C3">
-        <v>12592.05488639566</v>
+        <v>12527.97337185052</v>
       </c>
       <c r="D3">
-        <v>12644.86988639566</v>
+        <v>12707.80337185052</v>
       </c>
       <c r="E3">
-        <v>31.015</v>
+        <v>158.03</v>
       </c>
       <c r="F3">
-        <v>127.015</v>
+        <v>254.03</v>
       </c>
       <c r="G3">
         <v>74.2</v>
@@ -1658,28 +1658,28 @@
         <v>266.6</v>
       </c>
       <c r="M3">
-        <v>6.3888545</v>
+        <v>12.777709</v>
       </c>
       <c r="N3">
-        <v>260.2111455</v>
+        <v>253.822291</v>
       </c>
       <c r="O3">
-        <v>72.85912074000002</v>
+        <v>71.07024148000002</v>
       </c>
       <c r="P3">
-        <v>187.35202476</v>
+        <v>182.75204952</v>
       </c>
       <c r="Q3">
-        <v>253.05202476</v>
+        <v>248.45204952</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09116631830952683</v>
+        <v>0.09150055774303104</v>
       </c>
       <c r="T3">
-        <v>1.047720977125331</v>
+        <v>1.055440132633511</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>41.72892026262299</v>
+        <v>20.86446013131149</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09039486658817042</v>
+        <v>0.09017291804990929</v>
       </c>
       <c r="C4">
-        <v>12527.97337185052</v>
+        <v>12464.52143028449</v>
       </c>
       <c r="D4">
-        <v>12707.80337185052</v>
+        <v>12771.36643028449</v>
       </c>
       <c r="E4">
-        <v>158.03</v>
+        <v>285.045</v>
       </c>
       <c r="F4">
-        <v>254.03</v>
+        <v>381.045</v>
       </c>
       <c r="G4">
         <v>74.2</v>
@@ -1740,28 +1740,28 @@
         <v>266.6</v>
       </c>
       <c r="M4">
-        <v>12.777709</v>
+        <v>19.1665635</v>
       </c>
       <c r="N4">
-        <v>253.822291</v>
+        <v>247.4334365</v>
       </c>
       <c r="O4">
-        <v>71.07024148000002</v>
+        <v>69.28136222000002</v>
       </c>
       <c r="P4">
-        <v>182.75204952</v>
+        <v>178.15207428</v>
       </c>
       <c r="Q4">
-        <v>248.45204952</v>
+        <v>243.85207428</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09150055774303104</v>
+        <v>0.09184168871124669</v>
       </c>
       <c r="T4">
-        <v>1.055440132633511</v>
+        <v>1.063318445987222</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>20.86446013131149</v>
+        <v>13.90964008754099</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09017291804990929</v>
+        <v>0.08995096951164815</v>
       </c>
       <c r="C5">
-        <v>12464.52143028449</v>
+        <v>12401.70855635674</v>
       </c>
       <c r="D5">
-        <v>12771.36643028449</v>
+        <v>12835.56855635674</v>
       </c>
       <c r="E5">
-        <v>285.045</v>
+        <v>412.06</v>
       </c>
       <c r="F5">
-        <v>381.045</v>
+        <v>508.06</v>
       </c>
       <c r="G5">
         <v>74.2</v>
@@ -1822,28 +1822,28 @@
         <v>266.6</v>
       </c>
       <c r="M5">
-        <v>19.1665635</v>
+        <v>25.555418</v>
       </c>
       <c r="N5">
-        <v>247.4334365</v>
+        <v>241.044582</v>
       </c>
       <c r="O5">
-        <v>69.28136222000002</v>
+        <v>67.49248296000002</v>
       </c>
       <c r="P5">
-        <v>178.15207428</v>
+        <v>173.55209904</v>
       </c>
       <c r="Q5">
-        <v>243.85207428</v>
+        <v>239.25209904</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09184168871124669</v>
+        <v>0.09218992657463349</v>
       </c>
       <c r="T5">
-        <v>1.063318445987222</v>
+        <v>1.071360890869134</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>13.90964008754099</v>
+        <v>10.43223006565575</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08995096951164815</v>
+        <v>0.089783020973387</v>
       </c>
       <c r="C6">
-        <v>12401.70855635674</v>
+        <v>12323.70599181667</v>
       </c>
       <c r="D6">
-        <v>12835.56855635674</v>
+        <v>12884.58099181667</v>
       </c>
       <c r="E6">
-        <v>412.06</v>
+        <v>539.075</v>
       </c>
       <c r="F6">
-        <v>508.06</v>
+        <v>635.075</v>
       </c>
       <c r="G6">
         <v>74.2</v>
@@ -1904,45 +1904,45 @@
         <v>266.6</v>
       </c>
       <c r="M6">
-        <v>25.555418</v>
+        <v>32.896885</v>
       </c>
       <c r="N6">
-        <v>241.044582</v>
+        <v>233.703115</v>
       </c>
       <c r="O6">
-        <v>67.49248296000002</v>
+        <v>65.43687220000001</v>
       </c>
       <c r="P6">
-        <v>173.55209904</v>
+        <v>168.2662428</v>
       </c>
       <c r="Q6">
-        <v>239.25209904</v>
+        <v>233.9662428</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09218992657463349</v>
+        <v>0.09254549576146001</v>
       </c>
       <c r="T6">
-        <v>1.071360890869134</v>
+        <v>1.079572650380139</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.28</v>
       </c>
       <c r="W6">
-        <v>0.036216</v>
+        <v>0.037296</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>10.43223006565575</v>
+        <v>8.104110769150331</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.089783020973387</v>
+        <v>0.08957187243512588</v>
       </c>
       <c r="C7">
-        <v>12323.70599181667</v>
+        <v>12258.84415756395</v>
       </c>
       <c r="D7">
-        <v>12884.58099181667</v>
+        <v>12946.73415756395</v>
       </c>
       <c r="E7">
-        <v>539.075</v>
+        <v>666.09</v>
       </c>
       <c r="F7">
-        <v>635.075</v>
+        <v>762.09</v>
       </c>
       <c r="G7">
         <v>74.2</v>
@@ -1986,28 +1986,28 @@
         <v>266.6</v>
       </c>
       <c r="M7">
-        <v>32.896885</v>
+        <v>39.476262</v>
       </c>
       <c r="N7">
-        <v>233.703115</v>
+        <v>227.123738</v>
       </c>
       <c r="O7">
-        <v>65.43687220000001</v>
+        <v>63.59464664000001</v>
       </c>
       <c r="P7">
-        <v>168.2662428</v>
+        <v>163.52909136</v>
       </c>
       <c r="Q7">
-        <v>233.9662428</v>
+        <v>229.22909136</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09254549576146001</v>
+        <v>0.09290863025013391</v>
       </c>
       <c r="T7">
-        <v>1.079572650380139</v>
+        <v>1.087959128178612</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>8.104110769150331</v>
+        <v>6.753425640958611</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08957187243512588</v>
+        <v>0.08944640389686474</v>
       </c>
       <c r="C8">
-        <v>12258.84415756395</v>
+        <v>12169.04660653966</v>
       </c>
       <c r="D8">
-        <v>12946.73415756395</v>
+        <v>12983.95160653966</v>
       </c>
       <c r="E8">
-        <v>666.0899999999999</v>
+        <v>793.1049999999999</v>
       </c>
       <c r="F8">
-        <v>762.0899999999999</v>
+        <v>889.1049999999999</v>
       </c>
       <c r="G8">
         <v>74.2</v>
@@ -2068,45 +2068,45 @@
         <v>266.6</v>
       </c>
       <c r="M8">
-        <v>39.476262</v>
+        <v>47.56711749999999</v>
       </c>
       <c r="N8">
-        <v>227.123738</v>
+        <v>219.0328825</v>
       </c>
       <c r="O8">
-        <v>63.59464664000001</v>
+        <v>61.32920710000001</v>
       </c>
       <c r="P8">
-        <v>163.52909136</v>
+        <v>157.7036754</v>
       </c>
       <c r="Q8">
-        <v>229.22909136</v>
+        <v>223.4036754</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09290863025013391</v>
+        <v>0.09327957408265025</v>
       </c>
       <c r="T8">
-        <v>1.087959128178612</v>
+        <v>1.096525960338343</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.28</v>
       </c>
       <c r="W8">
-        <v>0.037296</v>
+        <v>0.03852</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.753425640958611</v>
+        <v>5.604712120720791</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08944640389686473</v>
+        <v>0.08929357535860359</v>
       </c>
       <c r="C9">
-        <v>12169.04660653967</v>
+        <v>12087.65485844573</v>
       </c>
       <c r="D9">
-        <v>12983.95160653967</v>
+        <v>13029.57485844573</v>
       </c>
       <c r="E9">
-        <v>793.1050000000001</v>
+        <v>920.12</v>
       </c>
       <c r="F9">
-        <v>889.1050000000001</v>
+        <v>1016.12</v>
       </c>
       <c r="G9">
         <v>74.2</v>
@@ -2150,45 +2150,45 @@
         <v>266.6</v>
       </c>
       <c r="M9">
-        <v>47.56711750000001</v>
+        <v>55.175316</v>
       </c>
       <c r="N9">
-        <v>219.0328825</v>
+        <v>211.424684</v>
       </c>
       <c r="O9">
-        <v>61.32920710000001</v>
+        <v>59.19891152000001</v>
       </c>
       <c r="P9">
-        <v>157.7036754</v>
+        <v>152.22577248</v>
       </c>
       <c r="Q9">
-        <v>223.4036754</v>
+        <v>217.92577248</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09327957408265025</v>
+        <v>0.09365858191152565</v>
       </c>
       <c r="T9">
-        <v>1.096525960338343</v>
+        <v>1.105279027979807</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.28</v>
       </c>
       <c r="W9">
-        <v>0.03852</v>
+        <v>0.039096</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>5.60471212072079</v>
+        <v>4.831870831514586</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08929357535860359</v>
+        <v>0.08910042682034246</v>
       </c>
       <c r="C10">
-        <v>12087.65485844573</v>
+        <v>12018.76037879336</v>
       </c>
       <c r="D10">
-        <v>13029.57485844573</v>
+        <v>13087.69537879336</v>
       </c>
       <c r="E10">
-        <v>920.12</v>
+        <v>1047.135</v>
       </c>
       <c r="F10">
-        <v>1016.12</v>
+        <v>1143.135</v>
       </c>
       <c r="G10">
         <v>74.2</v>
@@ -2232,28 +2232,28 @@
         <v>266.6</v>
       </c>
       <c r="M10">
-        <v>55.175316</v>
+        <v>62.0722305</v>
       </c>
       <c r="N10">
-        <v>211.424684</v>
+        <v>204.5277695</v>
       </c>
       <c r="O10">
-        <v>59.19891152000001</v>
+        <v>57.26777546000002</v>
       </c>
       <c r="P10">
-        <v>152.22577248</v>
+        <v>147.25999404</v>
       </c>
       <c r="Q10">
-        <v>217.92577248</v>
+        <v>212.95999404</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09365858191152565</v>
+        <v>0.0940459195827939</v>
       </c>
       <c r="T10">
-        <v>1.105279027979807</v>
+        <v>1.11422447073427</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>4.831870831514586</v>
+        <v>4.294996294679631</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08910042682034246</v>
+        <v>0.08897927828208133</v>
       </c>
       <c r="C11">
-        <v>12018.76037879336</v>
+        <v>11928.46565822901</v>
       </c>
       <c r="D11">
-        <v>13087.69537879336</v>
+        <v>13124.41565822901</v>
       </c>
       <c r="E11">
-        <v>1047.135</v>
+        <v>1174.15</v>
       </c>
       <c r="F11">
-        <v>1143.135</v>
+        <v>1270.15</v>
       </c>
       <c r="G11">
         <v>74.2</v>
@@ -2314,45 +2314,45 @@
         <v>266.6</v>
       </c>
       <c r="M11">
-        <v>62.0722305</v>
+        <v>70.239295</v>
       </c>
       <c r="N11">
-        <v>204.5277695</v>
+        <v>196.360705</v>
       </c>
       <c r="O11">
-        <v>57.26777546000002</v>
+        <v>54.98099740000001</v>
       </c>
       <c r="P11">
-        <v>147.25999404</v>
+        <v>141.3797076</v>
       </c>
       <c r="Q11">
-        <v>212.95999404</v>
+        <v>207.0797076</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0940459195827939</v>
+        <v>0.09444186475786813</v>
       </c>
       <c r="T11">
-        <v>1.11422447073427</v>
+        <v>1.1233687011055</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.28</v>
       </c>
       <c r="W11">
-        <v>0.039096</v>
+        <v>0.039816</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.294996294679631</v>
+        <v>3.795596183019776</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08897927828208133</v>
+        <v>0.08879332974382018</v>
       </c>
       <c r="C12">
-        <v>11928.46565822901</v>
+        <v>11858.21448465793</v>
       </c>
       <c r="D12">
-        <v>13124.41565822901</v>
+        <v>13181.17948465793</v>
       </c>
       <c r="E12">
-        <v>1174.15</v>
+        <v>1301.165</v>
       </c>
       <c r="F12">
-        <v>1270.15</v>
+        <v>1397.165</v>
       </c>
       <c r="G12">
         <v>74.2</v>
@@ -2396,28 +2396,28 @@
         <v>266.6</v>
       </c>
       <c r="M12">
-        <v>70.23929500000001</v>
+        <v>77.26322450000001</v>
       </c>
       <c r="N12">
-        <v>196.360705</v>
+        <v>189.3367755</v>
       </c>
       <c r="O12">
-        <v>54.98099740000001</v>
+        <v>53.01429714000001</v>
       </c>
       <c r="P12">
-        <v>141.3797076</v>
+        <v>136.32247836</v>
       </c>
       <c r="Q12">
-        <v>207.0797076</v>
+        <v>202.02247836</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09444186475786813</v>
+        <v>0.09484670757732604</v>
       </c>
       <c r="T12">
-        <v>1.1233687011055</v>
+        <v>1.132718419799678</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.795596183019775</v>
+        <v>3.450541984563432</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08879332974382018</v>
+        <v>0.08860738120555903</v>
       </c>
       <c r="C13">
-        <v>11858.21448465793</v>
+        <v>11788.45645737393</v>
       </c>
       <c r="D13">
-        <v>13181.17948465793</v>
+        <v>13238.43645737393</v>
       </c>
       <c r="E13">
-        <v>1301.165</v>
+        <v>1428.18</v>
       </c>
       <c r="F13">
-        <v>1397.165</v>
+        <v>1524.18</v>
       </c>
       <c r="G13">
         <v>74.2</v>
@@ -2478,28 +2478,28 @@
         <v>266.6</v>
       </c>
       <c r="M13">
-        <v>77.26322450000001</v>
+        <v>84.28715399999999</v>
       </c>
       <c r="N13">
-        <v>189.3367755</v>
+        <v>182.312846</v>
       </c>
       <c r="O13">
-        <v>53.01429714000001</v>
+        <v>51.04759688000001</v>
       </c>
       <c r="P13">
-        <v>136.32247836</v>
+        <v>131.26524912</v>
       </c>
       <c r="Q13">
-        <v>202.02247836</v>
+        <v>196.96524912</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09484670757732604</v>
+        <v>0.09526075136995343</v>
       </c>
       <c r="T13">
-        <v>1.132718419799678</v>
+        <v>1.142280632100541</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.450541984563432</v>
+        <v>3.162996819183147</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08860738120555903</v>
+        <v>0.08865543266729789</v>
       </c>
       <c r="C14">
-        <v>11788.45645737393</v>
+        <v>11646.5979198497</v>
       </c>
       <c r="D14">
-        <v>13238.43645737393</v>
+        <v>13223.5929198497</v>
       </c>
       <c r="E14">
-        <v>1428.18</v>
+        <v>1555.195</v>
       </c>
       <c r="F14">
-        <v>1524.18</v>
+        <v>1651.195</v>
       </c>
       <c r="G14">
         <v>74.2</v>
@@ -2560,45 +2560,45 @@
         <v>266.6</v>
       </c>
       <c r="M14">
-        <v>84.28715399999999</v>
+        <v>95.43907100000001</v>
       </c>
       <c r="N14">
-        <v>182.312846</v>
+        <v>171.160929</v>
       </c>
       <c r="O14">
-        <v>51.04759688000001</v>
+        <v>47.92506012</v>
       </c>
       <c r="P14">
-        <v>131.26524912</v>
+        <v>123.23586888</v>
       </c>
       <c r="Q14">
-        <v>196.96524912</v>
+        <v>188.93586888</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09526075136995343</v>
+        <v>0.09568431341068723</v>
       </c>
       <c r="T14">
-        <v>1.142280632100541</v>
+        <v>1.152062665373839</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.28</v>
       </c>
       <c r="W14">
-        <v>0.039816</v>
+        <v>0.041616</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.162996819183147</v>
+        <v>2.793405229185435</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08865543266729789</v>
+        <v>0.08848748412903676</v>
       </c>
       <c r="C15">
-        <v>11646.5979198497</v>
+        <v>11571.6094832971</v>
       </c>
       <c r="D15">
-        <v>13223.5929198497</v>
+        <v>13275.6194832971</v>
       </c>
       <c r="E15">
-        <v>1555.195</v>
+        <v>1682.21</v>
       </c>
       <c r="F15">
-        <v>1651.195</v>
+        <v>1778.21</v>
       </c>
       <c r="G15">
         <v>74.2</v>
@@ -2642,28 +2642,28 @@
         <v>266.6</v>
       </c>
       <c r="M15">
-        <v>95.43907100000001</v>
+        <v>102.780538</v>
       </c>
       <c r="N15">
-        <v>171.160929</v>
+        <v>163.819462</v>
       </c>
       <c r="O15">
-        <v>47.92506012</v>
+        <v>45.86944936</v>
       </c>
       <c r="P15">
-        <v>123.23586888</v>
+        <v>117.95001264</v>
       </c>
       <c r="Q15">
-        <v>188.93586888</v>
+        <v>183.65001264</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09568431341068723</v>
+        <v>0.09611772573143809</v>
       </c>
       <c r="T15">
-        <v>1.152062665373839</v>
+        <v>1.162072187793027</v>
       </c>
       <c r="U15">
         <v>0.0578</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>2.793405229185435</v>
+        <v>2.593876284243618</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08848748412903676</v>
+        <v>0.0886975355907756</v>
       </c>
       <c r="C16">
-        <v>11571.6094832971</v>
+        <v>11379.58927403387</v>
       </c>
       <c r="D16">
-        <v>13275.6194832971</v>
+        <v>13210.61427403387</v>
       </c>
       <c r="E16">
-        <v>1682.21</v>
+        <v>1809.225</v>
       </c>
       <c r="F16">
-        <v>1778.21</v>
+        <v>1905.225</v>
       </c>
       <c r="G16">
         <v>74.2</v>
@@ -2724,45 +2724,45 @@
         <v>266.6</v>
       </c>
       <c r="M16">
-        <v>102.780538</v>
+        <v>116.7902925</v>
       </c>
       <c r="N16">
-        <v>163.819462</v>
+        <v>149.8097075</v>
       </c>
       <c r="O16">
-        <v>45.86944936</v>
+        <v>41.94671810000001</v>
       </c>
       <c r="P16">
-        <v>117.95001264</v>
+        <v>107.8629894</v>
       </c>
       <c r="Q16">
-        <v>183.65001264</v>
+        <v>173.5629894</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09611772573143809</v>
+        <v>0.09656133598914778</v>
       </c>
       <c r="T16">
-        <v>1.162072187793027</v>
+        <v>1.172317228386785</v>
       </c>
       <c r="U16">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V16">
         <v>0.28</v>
       </c>
       <c r="W16">
-        <v>0.041616</v>
+        <v>0.044136</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.593876284243618</v>
+        <v>2.282723968689435</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0886975355907756</v>
+        <v>0.08887734705251447</v>
       </c>
       <c r="C17">
-        <v>11379.58927403387</v>
+        <v>11197.43114137562</v>
       </c>
       <c r="D17">
-        <v>13210.61427403387</v>
+        <v>13155.47114137562</v>
       </c>
       <c r="E17">
-        <v>1809.225</v>
+        <v>1936.24</v>
       </c>
       <c r="F17">
-        <v>1905.225</v>
+        <v>2032.24</v>
       </c>
       <c r="G17">
         <v>74.2</v>
@@ -2806,45 +2806,45 @@
         <v>266.6</v>
       </c>
       <c r="M17">
-        <v>116.7902925</v>
+        <v>130.266584</v>
       </c>
       <c r="N17">
-        <v>149.8097075</v>
+        <v>136.333416</v>
       </c>
       <c r="O17">
-        <v>41.94671810000001</v>
+        <v>38.17335648</v>
       </c>
       <c r="P17">
-        <v>107.8629894</v>
+        <v>98.16005952</v>
       </c>
       <c r="Q17">
-        <v>173.5629894</v>
+        <v>163.86005952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09656133598914778</v>
+        <v>0.09701550839585057</v>
       </c>
       <c r="T17">
-        <v>1.172317228386785</v>
+        <v>1.182806198518489</v>
       </c>
       <c r="U17">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V17">
         <v>0.28</v>
       </c>
       <c r="W17">
-        <v>0.044136</v>
+        <v>0.046152</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.282723968689436</v>
+        <v>2.046572434877082</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08887734705251447</v>
+        <v>0.09018683851425331</v>
       </c>
       <c r="C18">
-        <v>11197.43114137562</v>
+        <v>10682.30611346157</v>
       </c>
       <c r="D18">
-        <v>13155.47114137562</v>
+        <v>12767.36111346157</v>
       </c>
       <c r="E18">
-        <v>1936.24</v>
+        <v>2063.255</v>
       </c>
       <c r="F18">
-        <v>2032.24</v>
+        <v>2159.255</v>
       </c>
       <c r="G18">
         <v>74.2</v>
@@ -2888,45 +2888,45 @@
         <v>266.6</v>
       </c>
       <c r="M18">
-        <v>130.266584</v>
+        <v>163.671529</v>
       </c>
       <c r="N18">
-        <v>136.333416</v>
+        <v>102.928471</v>
       </c>
       <c r="O18">
-        <v>38.17335648</v>
+        <v>28.81997188</v>
       </c>
       <c r="P18">
-        <v>98.16005952</v>
+        <v>74.10849912</v>
       </c>
       <c r="Q18">
-        <v>163.86005952</v>
+        <v>139.80849912</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09701550839585057</v>
+        <v>0.09748062471596786</v>
       </c>
       <c r="T18">
-        <v>1.182806198518489</v>
+        <v>1.193547914918426</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V18">
         <v>0.28</v>
       </c>
       <c r="W18">
-        <v>0.046152</v>
+        <v>0.054576</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.046572434877082</v>
+        <v>1.628872178495992</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09018683851425331</v>
+        <v>0.09014848997599219</v>
       </c>
       <c r="C19">
-        <v>10682.30611346157</v>
+        <v>10566.33116547728</v>
       </c>
       <c r="D19">
-        <v>12767.36111346157</v>
+        <v>12778.40116547728</v>
       </c>
       <c r="E19">
-        <v>2063.255</v>
+        <v>2190.27</v>
       </c>
       <c r="F19">
-        <v>2159.255</v>
+        <v>2286.27</v>
       </c>
       <c r="G19">
         <v>74.2</v>
@@ -2970,28 +2970,28 @@
         <v>266.6</v>
       </c>
       <c r="M19">
-        <v>163.671529</v>
+        <v>173.299266</v>
       </c>
       <c r="N19">
-        <v>102.928471</v>
+        <v>93.30073399999998</v>
       </c>
       <c r="O19">
-        <v>28.81997188</v>
+        <v>26.12420552</v>
       </c>
       <c r="P19">
-        <v>74.10849912</v>
+        <v>67.17652847999997</v>
       </c>
       <c r="Q19">
-        <v>139.80849912</v>
+        <v>132.87652848</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09748062471596786</v>
+        <v>0.09795708533657585</v>
       </c>
       <c r="T19">
-        <v>1.193547914918426</v>
+        <v>1.20455162440129</v>
       </c>
       <c r="U19">
         <v>0.07580000000000001</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.628872178495992</v>
+        <v>1.538379279690659</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0901484899759922</v>
+        <v>0.09656181288213921</v>
       </c>
       <c r="C20">
-        <v>10566.33116547728</v>
+        <v>8824.873964825965</v>
       </c>
       <c r="D20">
-        <v>12778.40116547728</v>
+        <v>11163.95896482596</v>
       </c>
       <c r="E20">
-        <v>2190.27</v>
+        <v>2317.285</v>
       </c>
       <c r="F20">
-        <v>2286.27</v>
+        <v>2413.285</v>
       </c>
       <c r="G20">
         <v>74.2</v>
@@ -3052,45 +3052,45 @@
         <v>266.6</v>
       </c>
       <c r="M20">
-        <v>173.299266</v>
+        <v>286.215601</v>
       </c>
       <c r="N20">
-        <v>93.30073400000001</v>
+        <v>-19.61560099999997</v>
       </c>
       <c r="O20">
-        <v>26.12420552</v>
+        <v>-5.492368279999992</v>
       </c>
       <c r="P20">
-        <v>67.17652848</v>
+        <v>-14.12323271999998</v>
       </c>
       <c r="Q20">
-        <v>132.87652848</v>
+        <v>51.57676728000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09795708533657585</v>
+        <v>0.09864804199003335</v>
       </c>
       <c r="T20">
-        <v>1.20455162440129</v>
+        <v>1.220509052887606</v>
       </c>
       <c r="U20">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V20">
-        <v>0.28</v>
+        <v>0.2608103811923236</v>
       </c>
       <c r="W20">
-        <v>0.054576</v>
+        <v>0.08766788879059041</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.538379279690659</v>
+        <v>0.9314656471154416</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09656181288213921</v>
+        <v>0.0972898128821392</v>
       </c>
       <c r="C21">
-        <v>8824.873964825965</v>
+        <v>8540.014885163124</v>
       </c>
       <c r="D21">
-        <v>11163.95896482596</v>
+        <v>11006.11488516312</v>
       </c>
       <c r="E21">
-        <v>2317.285</v>
+        <v>2444.3</v>
       </c>
       <c r="F21">
-        <v>2413.285</v>
+        <v>2540.3</v>
       </c>
       <c r="G21">
         <v>74.2</v>
@@ -3134,37 +3134,37 @@
         <v>266.6</v>
       </c>
       <c r="M21">
-        <v>286.215601</v>
+        <v>301.2795800000001</v>
       </c>
       <c r="N21">
-        <v>-19.61560099999997</v>
+        <v>-34.67958000000004</v>
       </c>
       <c r="O21">
-        <v>-5.492368279999992</v>
+        <v>-9.710282400000013</v>
       </c>
       <c r="P21">
-        <v>-14.12323271999998</v>
+        <v>-24.96929760000003</v>
       </c>
       <c r="Q21">
-        <v>51.57676728000001</v>
+        <v>40.73070239999996</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09864804199003335</v>
+        <v>0.09930864251490876</v>
       </c>
       <c r="T21">
-        <v>1.220509052887606</v>
+        <v>1.235765416048701</v>
       </c>
       <c r="U21">
         <v>0.1186</v>
       </c>
       <c r="V21">
-        <v>0.2608103811923236</v>
+        <v>0.2477698621327074</v>
       </c>
       <c r="W21">
-        <v>0.08766788879059041</v>
+        <v>0.08921449435106092</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.9314656471154416</v>
+        <v>0.8848923647596693</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0972898128821392</v>
+        <v>0.0980178128821392</v>
       </c>
       <c r="C22">
-        <v>8540.014885163124</v>
+        <v>8259.557004388247</v>
       </c>
       <c r="D22">
-        <v>11006.11488516312</v>
+        <v>10852.67200438825</v>
       </c>
       <c r="E22">
-        <v>2444.3</v>
+        <v>2571.315</v>
       </c>
       <c r="F22">
-        <v>2540.3</v>
+        <v>2667.315</v>
       </c>
       <c r="G22">
         <v>74.2</v>
@@ -3216,37 +3216,37 @@
         <v>266.6</v>
       </c>
       <c r="M22">
-        <v>301.2795800000001</v>
+        <v>316.343559</v>
       </c>
       <c r="N22">
-        <v>-34.67958000000004</v>
+        <v>-49.743559</v>
       </c>
       <c r="O22">
-        <v>-9.710282400000013</v>
+        <v>-13.92819652</v>
       </c>
       <c r="P22">
-        <v>-24.96929760000003</v>
+        <v>-35.81536248</v>
       </c>
       <c r="Q22">
-        <v>40.73070239999996</v>
+        <v>29.88463751999998</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09930864251490876</v>
+        <v>0.09998596710370508</v>
       </c>
       <c r="T22">
-        <v>1.235765416048701</v>
+        <v>1.251408016251849</v>
       </c>
       <c r="U22">
         <v>0.1186</v>
       </c>
       <c r="V22">
-        <v>0.2477698621327074</v>
+        <v>0.2359712972692452</v>
       </c>
       <c r="W22">
-        <v>0.08921449435106092</v>
+        <v>0.09061380414386754</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.8848923647596693</v>
+        <v>0.8427546331044471</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0980178128821392</v>
+        <v>0.0987458128821392</v>
       </c>
       <c r="C23">
-        <v>8259.557004388247</v>
+        <v>7983.318774275942</v>
       </c>
       <c r="D23">
-        <v>10852.67200438825</v>
+        <v>10703.44877427594</v>
       </c>
       <c r="E23">
-        <v>2571.315</v>
+        <v>2698.33</v>
       </c>
       <c r="F23">
-        <v>2667.315</v>
+        <v>2794.33</v>
       </c>
       <c r="G23">
         <v>74.2</v>
@@ -3298,37 +3298,37 @@
         <v>266.6</v>
       </c>
       <c r="M23">
-        <v>316.343559</v>
+        <v>331.407538</v>
       </c>
       <c r="N23">
-        <v>-49.743559</v>
+        <v>-64.80753800000002</v>
       </c>
       <c r="O23">
-        <v>-13.92819652</v>
+        <v>-18.14611064000001</v>
       </c>
       <c r="P23">
-        <v>-35.81536248</v>
+        <v>-46.66142736000002</v>
       </c>
       <c r="Q23">
-        <v>29.88463751999998</v>
+        <v>19.03857263999997</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09998596710370508</v>
+        <v>0.10068065898965</v>
       </c>
       <c r="T23">
-        <v>1.251408016251849</v>
+        <v>1.267451708767899</v>
       </c>
       <c r="U23">
         <v>0.1186</v>
       </c>
       <c r="V23">
-        <v>0.2359712972692452</v>
+        <v>0.2252453292115522</v>
       </c>
       <c r="W23">
-        <v>0.09061380414386754</v>
+        <v>0.09188590395550993</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8427546331044471</v>
+        <v>0.8044476043269722</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0987458128821392</v>
+        <v>0.1192934485467674</v>
       </c>
       <c r="C24">
-        <v>7983.318774275942</v>
+        <v>4863.784439319425</v>
       </c>
       <c r="D24">
-        <v>10703.44877427594</v>
+        <v>7710.929439319425</v>
       </c>
       <c r="E24">
-        <v>2698.33</v>
+        <v>2825.345</v>
       </c>
       <c r="F24">
-        <v>2794.33</v>
+        <v>2921.345</v>
       </c>
       <c r="G24">
         <v>74.2</v>
@@ -3380,45 +3380,45 @@
         <v>266.6</v>
       </c>
       <c r="M24">
-        <v>331.407538</v>
+        <v>586.606076</v>
       </c>
       <c r="N24">
-        <v>-64.80753800000002</v>
+        <v>-320.006076</v>
       </c>
       <c r="O24">
-        <v>-18.14611064000001</v>
+        <v>-89.60170128000001</v>
       </c>
       <c r="P24">
-        <v>-46.66142736000002</v>
+        <v>-230.40437472</v>
       </c>
       <c r="Q24">
-        <v>19.03857263999997</v>
+        <v>-164.70437472</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.10068065898965</v>
+        <v>0.1025799346448769</v>
       </c>
       <c r="T24">
-        <v>1.267451708767899</v>
+        <v>1.311314887872445</v>
       </c>
       <c r="U24">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.2252453292115522</v>
+        <v>0.1272540518315395</v>
       </c>
       <c r="W24">
-        <v>0.09188590395550993</v>
+        <v>0.1752473863922269</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8044476043269722</v>
+        <v>0.4544787565412125</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1192934485467674</v>
+        <v>0.1208434485467674</v>
       </c>
       <c r="C25">
-        <v>4863.784439319425</v>
+        <v>4577.50249646969</v>
       </c>
       <c r="D25">
-        <v>7710.929439319425</v>
+        <v>7551.662496469689</v>
       </c>
       <c r="E25">
-        <v>2825.345</v>
+        <v>2952.36</v>
       </c>
       <c r="F25">
-        <v>2921.345</v>
+        <v>3048.36</v>
       </c>
       <c r="G25">
         <v>74.2</v>
@@ -3462,37 +3462,37 @@
         <v>266.6</v>
       </c>
       <c r="M25">
-        <v>586.606076</v>
+        <v>612.1106880000001</v>
       </c>
       <c r="N25">
-        <v>-320.006076</v>
+        <v>-345.5106880000001</v>
       </c>
       <c r="O25">
-        <v>-89.60170128000001</v>
+        <v>-96.74299264000003</v>
       </c>
       <c r="P25">
-        <v>-230.40437472</v>
+        <v>-248.7676953600001</v>
       </c>
       <c r="Q25">
-        <v>-164.70437472</v>
+        <v>-183.0676953600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1025799346448769</v>
+        <v>0.1033270390480989</v>
       </c>
       <c r="T25">
-        <v>1.311314887872445</v>
+        <v>1.328569031133925</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1272540518315395</v>
+        <v>0.121951799671892</v>
       </c>
       <c r="W25">
-        <v>0.1752473863922269</v>
+        <v>0.1763120786258841</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.4544787565412125</v>
+        <v>0.4355421416853286</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1208434485467674</v>
+        <v>0.1223934485467674</v>
       </c>
       <c r="C26">
-        <v>4577.50249646969</v>
+        <v>4297.666633959745</v>
       </c>
       <c r="D26">
-        <v>7551.662496469689</v>
+        <v>7398.841633959745</v>
       </c>
       <c r="E26">
-        <v>2952.36</v>
+        <v>3079.375</v>
       </c>
       <c r="F26">
-        <v>3048.36</v>
+        <v>3175.375</v>
       </c>
       <c r="G26">
         <v>74.2</v>
@@ -3544,37 +3544,37 @@
         <v>266.6</v>
       </c>
       <c r="M26">
-        <v>612.110688</v>
+        <v>637.6153</v>
       </c>
       <c r="N26">
-        <v>-345.510688</v>
+        <v>-371.0153</v>
       </c>
       <c r="O26">
-        <v>-96.74299264</v>
+        <v>-103.884284</v>
       </c>
       <c r="P26">
-        <v>-248.7676953599999</v>
+        <v>-267.131016</v>
       </c>
       <c r="Q26">
-        <v>-183.06769536</v>
+        <v>-201.431016</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1033270390480989</v>
+        <v>0.1040940662354069</v>
       </c>
       <c r="T26">
-        <v>1.328569031133925</v>
+        <v>1.346283284882377</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.121951799671892</v>
+        <v>0.1170737276850164</v>
       </c>
       <c r="W26">
-        <v>0.1763120786258841</v>
+        <v>0.1772915954808487</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4355421416853287</v>
+        <v>0.4181204560179155</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1223934485467674</v>
+        <v>0.1239434485467674</v>
       </c>
       <c r="C27">
-        <v>4297.666633959745</v>
+        <v>4023.893271666914</v>
       </c>
       <c r="D27">
-        <v>7398.841633959745</v>
+        <v>7252.083271666915</v>
       </c>
       <c r="E27">
-        <v>3079.375</v>
+        <v>3206.39</v>
       </c>
       <c r="F27">
-        <v>3175.375</v>
+        <v>3302.39</v>
       </c>
       <c r="G27">
         <v>74.2</v>
@@ -3626,37 +3626,37 @@
         <v>266.6</v>
       </c>
       <c r="M27">
-        <v>637.6153</v>
+        <v>663.1199120000001</v>
       </c>
       <c r="N27">
-        <v>-371.0153</v>
+        <v>-396.5199120000001</v>
       </c>
       <c r="O27">
-        <v>-103.884284</v>
+        <v>-111.02557536</v>
       </c>
       <c r="P27">
-        <v>-267.131016</v>
+        <v>-285.49433664</v>
       </c>
       <c r="Q27">
-        <v>-201.431016</v>
+        <v>-219.79433664</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1040940662354069</v>
+        <v>0.1048818238872368</v>
       </c>
       <c r="T27">
-        <v>1.346283284882377</v>
+        <v>1.364476302245653</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1170737276850164</v>
+        <v>0.1125708920048234</v>
       </c>
       <c r="W27">
-        <v>0.1772915954808487</v>
+        <v>0.1781957648854315</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4181204560179155</v>
+        <v>0.4020389000172264</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1239434485467674</v>
+        <v>0.1254934485467674</v>
       </c>
       <c r="C28">
-        <v>4023.893271666914</v>
+        <v>3755.82867127866</v>
       </c>
       <c r="D28">
-        <v>7252.083271666915</v>
+        <v>7111.03367127866</v>
       </c>
       <c r="E28">
-        <v>3206.39</v>
+        <v>3333.405</v>
       </c>
       <c r="F28">
-        <v>3302.39</v>
+        <v>3429.405</v>
       </c>
       <c r="G28">
         <v>74.2</v>
@@ -3708,37 +3708,37 @@
         <v>266.6</v>
       </c>
       <c r="M28">
-        <v>663.1199120000001</v>
+        <v>688.6245240000001</v>
       </c>
       <c r="N28">
-        <v>-396.5199120000001</v>
+        <v>-422.024524</v>
       </c>
       <c r="O28">
-        <v>-111.02557536</v>
+        <v>-118.16686672</v>
       </c>
       <c r="P28">
-        <v>-285.49433664</v>
+        <v>-303.85765728</v>
       </c>
       <c r="Q28">
-        <v>-219.79433664</v>
+        <v>-238.15765728</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1048818238872368</v>
+        <v>0.1056911639404866</v>
       </c>
       <c r="T28">
-        <v>1.364476302245653</v>
+        <v>1.383167758440798</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1125708920048234</v>
+        <v>0.1084015997083485</v>
       </c>
       <c r="W28">
-        <v>0.1781957648854315</v>
+        <v>0.1790329587785636</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4020389000172264</v>
+        <v>0.3871485703869588</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1254934485467674</v>
+        <v>0.1270434485467674</v>
       </c>
       <c r="C29">
-        <v>3755.82867127866</v>
+        <v>3493.146089613448</v>
       </c>
       <c r="D29">
-        <v>7111.03367127866</v>
+        <v>6975.366089613449</v>
       </c>
       <c r="E29">
-        <v>3333.405</v>
+        <v>3460.420000000001</v>
       </c>
       <c r="F29">
-        <v>3429.405</v>
+        <v>3556.420000000001</v>
       </c>
       <c r="G29">
         <v>74.2</v>
@@ -3790,37 +3790,37 @@
         <v>266.6</v>
       </c>
       <c r="M29">
-        <v>688.6245240000001</v>
+        <v>714.1291360000001</v>
       </c>
       <c r="N29">
-        <v>-422.024524</v>
+        <v>-447.5291360000001</v>
       </c>
       <c r="O29">
-        <v>-118.16686672</v>
+        <v>-125.30815808</v>
       </c>
       <c r="P29">
-        <v>-303.85765728</v>
+        <v>-322.2209779200001</v>
       </c>
       <c r="Q29">
-        <v>-238.15765728</v>
+        <v>-256.5209779200001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1056911639404866</v>
+        <v>0.1065229856618822</v>
       </c>
       <c r="T29">
-        <v>1.383167758440798</v>
+        <v>1.402378421752476</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1084015997083485</v>
+        <v>0.1045301140044789</v>
       </c>
       <c r="W29">
-        <v>0.1790329587785636</v>
+        <v>0.1798103531079006</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3871485703869588</v>
+        <v>0.3733218357302817</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1270434485467674</v>
+        <v>0.1285934485467674</v>
       </c>
       <c r="C30">
-        <v>3493.146089613448</v>
+        <v>3235.543251702653</v>
       </c>
       <c r="D30">
-        <v>6975.366089613449</v>
+        <v>6844.778251702654</v>
       </c>
       <c r="E30">
-        <v>3460.420000000001</v>
+        <v>3587.435</v>
       </c>
       <c r="F30">
-        <v>3556.420000000001</v>
+        <v>3683.435</v>
       </c>
       <c r="G30">
         <v>74.2</v>
@@ -3872,37 +3872,37 @@
         <v>266.6</v>
       </c>
       <c r="M30">
-        <v>714.1291360000001</v>
+        <v>739.6337480000001</v>
       </c>
       <c r="N30">
-        <v>-447.5291360000001</v>
+        <v>-473.0337480000001</v>
       </c>
       <c r="O30">
-        <v>-125.30815808</v>
+        <v>-132.44944944</v>
       </c>
       <c r="P30">
-        <v>-322.2209779200001</v>
+        <v>-340.58429856</v>
       </c>
       <c r="Q30">
-        <v>-256.5209779200001</v>
+        <v>-274.88429856</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1065229856618822</v>
+        <v>0.1073782389810637</v>
       </c>
       <c r="T30">
-        <v>1.402378421752476</v>
+        <v>1.422130230509553</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1045301140044789</v>
+        <v>0.1009256273146693</v>
       </c>
       <c r="W30">
-        <v>0.1798103531079006</v>
+        <v>0.1805341340352144</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3733218357302817</v>
+        <v>0.3604486689809616</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1285934485467674</v>
+        <v>0.1301434485467674</v>
       </c>
       <c r="C31">
-        <v>3235.543251702655</v>
+        <v>2982.740102499146</v>
       </c>
       <c r="D31">
-        <v>6844.778251702655</v>
+        <v>6718.990102499146</v>
       </c>
       <c r="E31">
-        <v>3587.435</v>
+        <v>3714.45</v>
       </c>
       <c r="F31">
-        <v>3683.435</v>
+        <v>3810.45</v>
       </c>
       <c r="G31">
         <v>74.2</v>
@@ -3954,37 +3954,37 @@
         <v>266.6</v>
       </c>
       <c r="M31">
-        <v>739.633748</v>
+        <v>765.13836</v>
       </c>
       <c r="N31">
-        <v>-473.0337479999999</v>
+        <v>-498.53836</v>
       </c>
       <c r="O31">
-        <v>-132.44944944</v>
+        <v>-139.5907408</v>
       </c>
       <c r="P31">
-        <v>-340.58429856</v>
+        <v>-358.9476192</v>
       </c>
       <c r="Q31">
-        <v>-274.88429856</v>
+        <v>-293.2476192</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1073782389810637</v>
+        <v>0.1082579281093646</v>
       </c>
       <c r="T31">
-        <v>1.422130230509553</v>
+        <v>1.44244637665969</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1009256273146693</v>
+        <v>0.09756143973751363</v>
       </c>
       <c r="W31">
-        <v>0.1805341340352144</v>
+        <v>0.1812096629007073</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3604486689809617</v>
+        <v>0.3484337133482629</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1301434485467674</v>
+        <v>0.1316934485467674</v>
       </c>
       <c r="C32">
-        <v>2982.740102499146</v>
+        <v>2734.47680201668</v>
       </c>
       <c r="D32">
-        <v>6718.990102499146</v>
+        <v>6597.741802016681</v>
       </c>
       <c r="E32">
-        <v>3714.45</v>
+        <v>3841.465</v>
       </c>
       <c r="F32">
-        <v>3810.45</v>
+        <v>3937.465</v>
       </c>
       <c r="G32">
         <v>74.2</v>
@@ -4036,37 +4036,37 @@
         <v>266.6</v>
       </c>
       <c r="M32">
-        <v>765.13836</v>
+        <v>790.6429720000001</v>
       </c>
       <c r="N32">
-        <v>-498.53836</v>
+        <v>-524.0429720000001</v>
       </c>
       <c r="O32">
-        <v>-139.5907408</v>
+        <v>-146.73203216</v>
       </c>
       <c r="P32">
-        <v>-358.9476192</v>
+        <v>-377.3109398400001</v>
       </c>
       <c r="Q32">
-        <v>-293.2476192</v>
+        <v>-311.6109398400001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1082579281093646</v>
+        <v>0.1091631154732684</v>
       </c>
       <c r="T32">
-        <v>1.44244637665969</v>
+        <v>1.46335139661128</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.09756143973751363</v>
+        <v>0.09441429652017447</v>
       </c>
       <c r="W32">
-        <v>0.1812096629007073</v>
+        <v>0.181841609258749</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3484337133482629</v>
+        <v>0.3371939161434803</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1316934485467674</v>
+        <v>0.1332434485467674</v>
       </c>
       <c r="C33">
-        <v>2734.47680201668</v>
+        <v>2490.511933695141</v>
       </c>
       <c r="D33">
-        <v>6597.741802016681</v>
+        <v>6480.791933695141</v>
       </c>
       <c r="E33">
-        <v>3841.465</v>
+        <v>3968.48</v>
       </c>
       <c r="F33">
-        <v>3937.465</v>
+        <v>4064.48</v>
       </c>
       <c r="G33">
         <v>74.2</v>
@@ -4118,37 +4118,37 @@
         <v>266.6</v>
       </c>
       <c r="M33">
-        <v>790.6429720000001</v>
+        <v>816.1475840000001</v>
       </c>
       <c r="N33">
-        <v>-524.0429720000001</v>
+        <v>-549.547584</v>
       </c>
       <c r="O33">
-        <v>-146.73203216</v>
+        <v>-153.87332352</v>
       </c>
       <c r="P33">
-        <v>-377.3109398400001</v>
+        <v>-395.67426048</v>
       </c>
       <c r="Q33">
-        <v>-311.6109398400001</v>
+        <v>-329.9742604800001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1091631154732684</v>
+        <v>0.1100949259949341</v>
       </c>
       <c r="T33">
-        <v>1.46335139661128</v>
+        <v>1.484871270090857</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.09441429652017447</v>
+        <v>0.09146384975391902</v>
       </c>
       <c r="W33">
-        <v>0.181841609258749</v>
+        <v>0.1824340589694131</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3371939161434803</v>
+        <v>0.3266566062639965</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1332434485467674</v>
+        <v>0.1347934485467674</v>
       </c>
       <c r="C34">
-        <v>2490.511933695141</v>
+        <v>2250.620899995325</v>
       </c>
       <c r="D34">
-        <v>6480.791933695141</v>
+        <v>6367.915899995325</v>
       </c>
       <c r="E34">
-        <v>3968.48</v>
+        <v>4095.495</v>
       </c>
       <c r="F34">
-        <v>4064.48</v>
+        <v>4191.495</v>
       </c>
       <c r="G34">
         <v>74.2</v>
@@ -4200,37 +4200,37 @@
         <v>266.6</v>
       </c>
       <c r="M34">
-        <v>816.1475840000001</v>
+        <v>841.652196</v>
       </c>
       <c r="N34">
-        <v>-549.547584</v>
+        <v>-575.052196</v>
       </c>
       <c r="O34">
-        <v>-153.87332352</v>
+        <v>-161.01461488</v>
       </c>
       <c r="P34">
-        <v>-395.67426048</v>
+        <v>-414.03758112</v>
       </c>
       <c r="Q34">
-        <v>-329.9742604800001</v>
+        <v>-348.33758112</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1100949259949341</v>
+        <v>0.1110545517560526</v>
       </c>
       <c r="T34">
-        <v>1.484871270090857</v>
+        <v>1.507033527853407</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.09146384975391902</v>
+        <v>0.08869221794319421</v>
       </c>
       <c r="W34">
-        <v>0.1824340589694131</v>
+        <v>0.1829906026370066</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3266566062639965</v>
+        <v>0.3167579212256936</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1347934485467674</v>
+        <v>0.1363434485467674</v>
       </c>
       <c r="C35">
-        <v>2250.620899995325</v>
+        <v>2014.594482787216</v>
       </c>
       <c r="D35">
-        <v>6367.915899995325</v>
+        <v>6258.904482787217</v>
       </c>
       <c r="E35">
-        <v>4095.495</v>
+        <v>4222.51</v>
       </c>
       <c r="F35">
-        <v>4191.495</v>
+        <v>4318.51</v>
       </c>
       <c r="G35">
         <v>74.2</v>
@@ -4282,37 +4282,37 @@
         <v>266.6</v>
       </c>
       <c r="M35">
-        <v>841.652196</v>
+        <v>867.1568080000001</v>
       </c>
       <c r="N35">
-        <v>-575.052196</v>
+        <v>-600.556808</v>
       </c>
       <c r="O35">
-        <v>-161.01461488</v>
+        <v>-168.15590624</v>
       </c>
       <c r="P35">
-        <v>-414.03758112</v>
+        <v>-432.40090176</v>
       </c>
       <c r="Q35">
-        <v>-348.33758112</v>
+        <v>-366.70090176</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1110545517560526</v>
+        <v>0.1120432570856897</v>
       </c>
       <c r="T35">
-        <v>1.507033527853407</v>
+        <v>1.529867369184519</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.08869221794319421</v>
+        <v>0.08608362329780614</v>
       </c>
       <c r="W35">
-        <v>0.1829906026370066</v>
+        <v>0.1835144084418005</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3167579212256936</v>
+        <v>0.307441511777879</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1363434485467674</v>
+        <v>0.1378934485467674</v>
       </c>
       <c r="C36">
-        <v>2014.594482787216</v>
+        <v>1782.237549116508</v>
       </c>
       <c r="D36">
-        <v>6258.904482787217</v>
+        <v>6153.562549116509</v>
       </c>
       <c r="E36">
-        <v>4222.51</v>
+        <v>4349.525000000001</v>
       </c>
       <c r="F36">
-        <v>4318.51</v>
+        <v>4445.525000000001</v>
       </c>
       <c r="G36">
         <v>74.2</v>
@@ -4364,37 +4364,37 @@
         <v>266.6</v>
       </c>
       <c r="M36">
-        <v>867.1568080000001</v>
+        <v>892.6614200000001</v>
       </c>
       <c r="N36">
-        <v>-600.556808</v>
+        <v>-626.0614200000001</v>
       </c>
       <c r="O36">
-        <v>-168.15590624</v>
+        <v>-175.2971976000001</v>
       </c>
       <c r="P36">
-        <v>-432.40090176</v>
+        <v>-450.7642224000001</v>
       </c>
       <c r="Q36">
-        <v>-366.70090176</v>
+        <v>-385.0642224000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1120432570856897</v>
+        <v>0.1130623841177772</v>
       </c>
       <c r="T36">
-        <v>1.529867369184519</v>
+        <v>1.553403790248897</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.08608362329780614</v>
+        <v>0.08362409120358309</v>
       </c>
       <c r="W36">
-        <v>0.1835144084418005</v>
+        <v>0.1840082824863205</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.307441511777879</v>
+        <v>0.2986574685842254</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1378934485467674</v>
+        <v>0.1394434485467674</v>
       </c>
       <c r="C37">
-        <v>1782.237549116508</v>
+        <v>1553.367885505236</v>
       </c>
       <c r="D37">
-        <v>6153.562549116509</v>
+        <v>6051.707885505237</v>
       </c>
       <c r="E37">
-        <v>4349.525000000001</v>
+        <v>4476.540000000001</v>
       </c>
       <c r="F37">
-        <v>4445.525000000001</v>
+        <v>4572.540000000001</v>
       </c>
       <c r="G37">
         <v>74.2</v>
@@ -4446,37 +4446,37 @@
         <v>266.6</v>
       </c>
       <c r="M37">
-        <v>892.6614200000001</v>
+        <v>918.1660320000002</v>
       </c>
       <c r="N37">
-        <v>-626.0614200000001</v>
+        <v>-651.5660320000002</v>
       </c>
       <c r="O37">
-        <v>-175.2971976000001</v>
+        <v>-182.4384889600001</v>
       </c>
       <c r="P37">
-        <v>-450.7642224000001</v>
+        <v>-469.1275430400001</v>
       </c>
       <c r="Q37">
-        <v>-385.0642224000001</v>
+        <v>-403.4275430400001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1130623841177772</v>
+        <v>0.1141133588696175</v>
       </c>
       <c r="T37">
-        <v>1.553403790248897</v>
+        <v>1.577675724471536</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.08362409120358309</v>
+        <v>0.08130119978126135</v>
       </c>
       <c r="W37">
-        <v>0.1840082824863205</v>
+        <v>0.1844747190839227</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2986574685842254</v>
+        <v>0.290361427790219</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1394434485467674</v>
+        <v>0.1409934485467674</v>
       </c>
       <c r="C38">
-        <v>1553.367885505237</v>
+        <v>1327.815146136285</v>
       </c>
       <c r="D38">
-        <v>6051.707885505237</v>
+        <v>5953.170146136285</v>
       </c>
       <c r="E38">
-        <v>4476.54</v>
+        <v>4603.555</v>
       </c>
       <c r="F38">
-        <v>4572.54</v>
+        <v>4699.555</v>
       </c>
       <c r="G38">
         <v>74.2</v>
@@ -4528,37 +4528,37 @@
         <v>266.6</v>
       </c>
       <c r="M38">
-        <v>918.166032</v>
+        <v>943.670644</v>
       </c>
       <c r="N38">
-        <v>-651.566032</v>
+        <v>-677.070644</v>
       </c>
       <c r="O38">
-        <v>-182.43848896</v>
+        <v>-189.57978032</v>
       </c>
       <c r="P38">
-        <v>-469.12754304</v>
+        <v>-487.49086368</v>
       </c>
       <c r="Q38">
-        <v>-403.42754304</v>
+        <v>-421.79086368</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1141133588696175</v>
+        <v>0.115197697899294</v>
       </c>
       <c r="T38">
-        <v>1.577675724471536</v>
+        <v>1.602718196288544</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08130119978126137</v>
+        <v>0.07910387005744347</v>
       </c>
       <c r="W38">
-        <v>0.1844747190839227</v>
+        <v>0.1849159428924654</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2903614277902191</v>
+        <v>0.2825138216337267</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1409934485467674</v>
+        <v>0.1425434485467674</v>
       </c>
       <c r="C39">
-        <v>1327.815146136285</v>
+        <v>1105.419902149524</v>
       </c>
       <c r="D39">
-        <v>5953.170146136285</v>
+        <v>5857.789902149524</v>
       </c>
       <c r="E39">
-        <v>4603.555</v>
+        <v>4730.57</v>
       </c>
       <c r="F39">
-        <v>4699.555</v>
+        <v>4826.57</v>
       </c>
       <c r="G39">
         <v>74.2</v>
@@ -4610,37 +4610,37 @@
         <v>266.6</v>
       </c>
       <c r="M39">
-        <v>943.670644</v>
+        <v>969.175256</v>
       </c>
       <c r="N39">
-        <v>-677.070644</v>
+        <v>-702.575256</v>
       </c>
       <c r="O39">
-        <v>-189.57978032</v>
+        <v>-196.72107168</v>
       </c>
       <c r="P39">
-        <v>-487.49086368</v>
+        <v>-505.8541843199999</v>
       </c>
       <c r="Q39">
-        <v>-421.79086368</v>
+        <v>-440.15418432</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.115197697899294</v>
+        <v>0.1163170156073471</v>
       </c>
       <c r="T39">
-        <v>1.602718196288544</v>
+        <v>1.628568489777069</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.07910387005744347</v>
+        <v>0.07702218926645814</v>
       </c>
       <c r="W39">
-        <v>0.1849159428924654</v>
+        <v>0.1853339443952952</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2825138216337267</v>
+        <v>0.2750792473802076</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1425434485467674</v>
+        <v>0.1440934485467674</v>
       </c>
       <c r="C40">
-        <v>1105.419902149524</v>
+        <v>886.0327808884449</v>
       </c>
       <c r="D40">
-        <v>5857.789902149524</v>
+        <v>5765.417780888445</v>
       </c>
       <c r="E40">
-        <v>4730.57</v>
+        <v>4857.585</v>
       </c>
       <c r="F40">
-        <v>4826.57</v>
+        <v>4953.585</v>
       </c>
       <c r="G40">
         <v>74.2</v>
@@ -4692,37 +4692,37 @@
         <v>266.6</v>
       </c>
       <c r="M40">
-        <v>969.175256</v>
+        <v>994.6798680000001</v>
       </c>
       <c r="N40">
-        <v>-702.575256</v>
+        <v>-728.079868</v>
       </c>
       <c r="O40">
-        <v>-196.72107168</v>
+        <v>-203.86236304</v>
       </c>
       <c r="P40">
-        <v>-505.8541843199999</v>
+        <v>-524.21750496</v>
       </c>
       <c r="Q40">
-        <v>-440.15418432</v>
+        <v>-458.5175049600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1163170156073471</v>
+        <v>0.1174730322566479</v>
       </c>
       <c r="T40">
-        <v>1.628568489777069</v>
+        <v>1.655266333871775</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.07702218926645814</v>
+        <v>0.07504726133654895</v>
       </c>
       <c r="W40">
-        <v>0.1853339443952952</v>
+        <v>0.185730509923621</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2750792473802076</v>
+        <v>0.2680259333448176</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1440934485467674</v>
+        <v>0.1456434485467674</v>
       </c>
       <c r="C41">
-        <v>886.0327808884449</v>
+        <v>669.5136853223594</v>
       </c>
       <c r="D41">
-        <v>5765.417780888445</v>
+        <v>5675.91368532236</v>
       </c>
       <c r="E41">
-        <v>4857.585</v>
+        <v>4984.6</v>
       </c>
       <c r="F41">
-        <v>4953.585</v>
+        <v>5080.6</v>
       </c>
       <c r="G41">
         <v>74.2</v>
@@ -4774,37 +4774,37 @@
         <v>266.6</v>
       </c>
       <c r="M41">
-        <v>994.6798680000001</v>
+        <v>1020.18448</v>
       </c>
       <c r="N41">
-        <v>-728.079868</v>
+        <v>-753.5844800000001</v>
       </c>
       <c r="O41">
-        <v>-203.86236304</v>
+        <v>-211.0036544</v>
       </c>
       <c r="P41">
-        <v>-524.21750496</v>
+        <v>-542.5808256</v>
       </c>
       <c r="Q41">
-        <v>-458.5175049600001</v>
+        <v>-476.8808256</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1174730322566479</v>
+        <v>0.1186675827942587</v>
       </c>
       <c r="T41">
-        <v>1.655266333871775</v>
+        <v>1.682854106102972</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.07504726133654895</v>
+        <v>0.07317107980313521</v>
       </c>
       <c r="W41">
-        <v>0.185730509923621</v>
+        <v>0.1861072471755305</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2680259333448176</v>
+        <v>0.2613252850111972</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1456434485467674</v>
+        <v>0.1471934485467674</v>
       </c>
       <c r="C42">
-        <v>669.5136853223594</v>
+        <v>455.7310850647191</v>
       </c>
       <c r="D42">
-        <v>5675.91368532236</v>
+        <v>5589.14608506472</v>
       </c>
       <c r="E42">
-        <v>4984.6</v>
+        <v>5111.615000000001</v>
       </c>
       <c r="F42">
-        <v>5080.6</v>
+        <v>5207.615000000001</v>
       </c>
       <c r="G42">
         <v>74.2</v>
@@ -4856,37 +4856,37 @@
         <v>266.6</v>
       </c>
       <c r="M42">
-        <v>1020.18448</v>
+        <v>1045.689092</v>
       </c>
       <c r="N42">
-        <v>-753.5844800000001</v>
+        <v>-779.0890920000001</v>
       </c>
       <c r="O42">
-        <v>-211.0036544</v>
+        <v>-218.14494576</v>
       </c>
       <c r="P42">
-        <v>-542.5808256</v>
+        <v>-560.94414624</v>
       </c>
       <c r="Q42">
-        <v>-476.8808256</v>
+        <v>-495.24414624</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1186675827942587</v>
+        <v>0.1199026265704325</v>
       </c>
       <c r="T42">
-        <v>1.682854106102972</v>
+        <v>1.711377057053869</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.07317107980313521</v>
+        <v>0.07138641932013193</v>
       </c>
       <c r="W42">
-        <v>0.1861072471755305</v>
+        <v>0.1864656070005175</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2613252850111972</v>
+        <v>0.2549514975718997</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1471934485467674</v>
+        <v>0.1487434485467674</v>
       </c>
       <c r="C43">
-        <v>455.7310850647191</v>
+        <v>244.5613714413967</v>
       </c>
       <c r="D43">
-        <v>5589.14608506472</v>
+        <v>5504.991371441397</v>
       </c>
       <c r="E43">
-        <v>5111.615000000001</v>
+        <v>5238.63</v>
       </c>
       <c r="F43">
-        <v>5207.615000000001</v>
+        <v>5334.63</v>
       </c>
       <c r="G43">
         <v>74.2</v>
@@ -4938,37 +4938,37 @@
         <v>266.6</v>
       </c>
       <c r="M43">
-        <v>1045.689092</v>
+        <v>1071.193704</v>
       </c>
       <c r="N43">
-        <v>-779.0890920000001</v>
+        <v>-804.593704</v>
       </c>
       <c r="O43">
-        <v>-218.14494576</v>
+        <v>-225.28623712</v>
       </c>
       <c r="P43">
-        <v>-560.94414624</v>
+        <v>-579.30746688</v>
       </c>
       <c r="Q43">
-        <v>-495.24414624</v>
+        <v>-513.6074668799999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1199026265704325</v>
+        <v>0.1211802580630262</v>
       </c>
       <c r="T43">
-        <v>1.711377057053869</v>
+        <v>1.740883558037557</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.07138641932013193</v>
+        <v>0.06968674266965259</v>
       </c>
       <c r="W43">
-        <v>0.1864656070005175</v>
+        <v>0.1868069020719338</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2549514975718997</v>
+        <v>0.2488812238201878</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1487434485467674</v>
+        <v>0.1502934485467674</v>
       </c>
       <c r="C44">
-        <v>244.5613714413967</v>
+        <v>35.8882699584592</v>
       </c>
       <c r="D44">
-        <v>5504.991371441397</v>
+        <v>5423.333269958459</v>
       </c>
       <c r="E44">
-        <v>5238.63</v>
+        <v>5365.645</v>
       </c>
       <c r="F44">
-        <v>5334.63</v>
+        <v>5461.645</v>
       </c>
       <c r="G44">
         <v>74.2</v>
@@ -5020,37 +5020,37 @@
         <v>266.6</v>
       </c>
       <c r="M44">
-        <v>1071.193704</v>
+        <v>1096.698316</v>
       </c>
       <c r="N44">
-        <v>-804.593704</v>
+        <v>-830.098316</v>
       </c>
       <c r="O44">
-        <v>-225.28623712</v>
+        <v>-232.42752848</v>
       </c>
       <c r="P44">
-        <v>-579.30746688</v>
+        <v>-597.67078752</v>
       </c>
       <c r="Q44">
-        <v>-513.6074668799999</v>
+        <v>-531.9707875199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1211802580630262</v>
+        <v>0.1225027187307986</v>
       </c>
       <c r="T44">
-        <v>1.740883558037557</v>
+        <v>1.771425374845233</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06968674266965259</v>
+        <v>0.06806612074710254</v>
       </c>
       <c r="W44">
-        <v>0.1868069020719338</v>
+        <v>0.1871323229539818</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2488812238201878</v>
+        <v>0.243093288382509</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1502934485467674</v>
+        <v>0.1518434485467674</v>
       </c>
       <c r="C45">
-        <v>35.8882699584592</v>
+        <v>-170.3976957035866</v>
       </c>
       <c r="D45">
-        <v>5423.333269958459</v>
+        <v>5344.062304296413</v>
       </c>
       <c r="E45">
-        <v>5365.645</v>
+        <v>5492.66</v>
       </c>
       <c r="F45">
-        <v>5461.645</v>
+        <v>5588.66</v>
       </c>
       <c r="G45">
         <v>74.2</v>
@@ -5102,37 +5102,37 @@
         <v>266.6</v>
       </c>
       <c r="M45">
-        <v>1096.698316</v>
+        <v>1122.202928</v>
       </c>
       <c r="N45">
-        <v>-830.098316</v>
+        <v>-855.6029279999999</v>
       </c>
       <c r="O45">
-        <v>-232.42752848</v>
+        <v>-239.56881984</v>
       </c>
       <c r="P45">
-        <v>-597.67078752</v>
+        <v>-616.03410816</v>
       </c>
       <c r="Q45">
-        <v>-531.9707875199999</v>
+        <v>-550.3341081599999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1225027187307986</v>
+        <v>0.1238724101367057</v>
       </c>
       <c r="T45">
-        <v>1.771425374845233</v>
+        <v>1.803057970824612</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.06806612074710254</v>
+        <v>0.06651916345739567</v>
       </c>
       <c r="W45">
-        <v>0.1871323229539818</v>
+        <v>0.187442951977755</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.243093288382509</v>
+        <v>0.2375684409192702</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1518434485467674</v>
+        <v>0.1533934485467674</v>
       </c>
       <c r="C46">
-        <v>-170.3976957035866</v>
+        <v>-374.3996933650551</v>
       </c>
       <c r="D46">
-        <v>5344.062304296413</v>
+        <v>5267.075306634945</v>
       </c>
       <c r="E46">
-        <v>5492.66</v>
+        <v>5619.675</v>
       </c>
       <c r="F46">
-        <v>5588.66</v>
+        <v>5715.675</v>
       </c>
       <c r="G46">
         <v>74.2</v>
@@ -5184,37 +5184,37 @@
         <v>266.6</v>
       </c>
       <c r="M46">
-        <v>1122.202928</v>
+        <v>1147.70754</v>
       </c>
       <c r="N46">
-        <v>-855.6029279999999</v>
+        <v>-881.1075400000001</v>
       </c>
       <c r="O46">
-        <v>-239.56881984</v>
+        <v>-246.7101112000001</v>
       </c>
       <c r="P46">
-        <v>-616.03410816</v>
+        <v>-634.3974288000001</v>
       </c>
       <c r="Q46">
-        <v>-550.3341081599999</v>
+        <v>-568.6974288000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1238724101367057</v>
+        <v>0.1252919085028276</v>
       </c>
       <c r="T46">
-        <v>1.803057970824612</v>
+        <v>1.835840843021423</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.06651916345739567</v>
+        <v>0.06504095982500908</v>
       </c>
       <c r="W46">
-        <v>0.187442951977755</v>
+        <v>0.1877397752671382</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2375684409192702</v>
+        <v>0.2322891422321752</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1533934485467674</v>
+        <v>0.1549434485467674</v>
       </c>
       <c r="C47">
-        <v>-374.3996933650551</v>
+        <v>-576.2150302976561</v>
       </c>
       <c r="D47">
-        <v>5267.075306634945</v>
+        <v>5192.274969702345</v>
       </c>
       <c r="E47">
-        <v>5619.675</v>
+        <v>5746.690000000001</v>
       </c>
       <c r="F47">
-        <v>5715.675</v>
+        <v>5842.690000000001</v>
       </c>
       <c r="G47">
         <v>74.2</v>
@@ -5266,37 +5266,37 @@
         <v>266.6</v>
       </c>
       <c r="M47">
-        <v>1147.70754</v>
+        <v>1173.212152</v>
       </c>
       <c r="N47">
-        <v>-881.1075400000001</v>
+        <v>-906.612152</v>
       </c>
       <c r="O47">
-        <v>-246.7101112000001</v>
+        <v>-253.85140256</v>
       </c>
       <c r="P47">
-        <v>-634.3974288000001</v>
+        <v>-652.76074944</v>
       </c>
       <c r="Q47">
-        <v>-568.6974288000001</v>
+        <v>-587.0607494400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1252919085028276</v>
+        <v>0.1267639808825096</v>
       </c>
       <c r="T47">
-        <v>1.835840843021423</v>
+        <v>1.869837895669968</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.06504095982500908</v>
+        <v>0.06362702591576976</v>
       </c>
       <c r="W47">
-        <v>0.1877397752671382</v>
+        <v>0.1880236931961135</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2322891422321752</v>
+        <v>0.2272393782706063</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1549434485467674</v>
+        <v>0.1564934485467674</v>
       </c>
       <c r="C48">
-        <v>-576.2150302976561</v>
+        <v>-775.935563540108</v>
       </c>
       <c r="D48">
-        <v>5192.274969702345</v>
+        <v>5119.569436459892</v>
       </c>
       <c r="E48">
-        <v>5746.690000000001</v>
+        <v>5873.705</v>
       </c>
       <c r="F48">
-        <v>5842.690000000001</v>
+        <v>5969.705</v>
       </c>
       <c r="G48">
         <v>74.2</v>
@@ -5348,37 +5348,37 @@
         <v>266.6</v>
       </c>
       <c r="M48">
-        <v>1173.212152</v>
+        <v>1198.716764</v>
       </c>
       <c r="N48">
-        <v>-906.612152</v>
+        <v>-932.116764</v>
       </c>
       <c r="O48">
-        <v>-253.85140256</v>
+        <v>-260.99269392</v>
       </c>
       <c r="P48">
-        <v>-652.76074944</v>
+        <v>-671.1240700799999</v>
       </c>
       <c r="Q48">
-        <v>-587.0607494400001</v>
+        <v>-605.4240700799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1267639808825096</v>
+        <v>0.1282916031633117</v>
       </c>
       <c r="T48">
-        <v>1.869837895669968</v>
+        <v>1.905117855965628</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.06362702591576976</v>
+        <v>0.0622732594069236</v>
       </c>
       <c r="W48">
-        <v>0.1880236931961135</v>
+        <v>0.1882955295110897</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2272393782706063</v>
+        <v>0.22240449788187</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1564934485467674</v>
+        <v>0.1580434485467674</v>
       </c>
       <c r="C49">
-        <v>-775.935563540108</v>
+        <v>-973.6480762168185</v>
       </c>
       <c r="D49">
-        <v>5119.569436459892</v>
+        <v>5048.871923783182</v>
       </c>
       <c r="E49">
-        <v>5873.705</v>
+        <v>6000.72</v>
       </c>
       <c r="F49">
-        <v>5969.705</v>
+        <v>6096.72</v>
       </c>
       <c r="G49">
         <v>74.2</v>
@@ -5430,37 +5430,37 @@
         <v>266.6</v>
       </c>
       <c r="M49">
-        <v>1198.716764</v>
+        <v>1224.221376</v>
       </c>
       <c r="N49">
-        <v>-932.116764</v>
+        <v>-957.6213760000002</v>
       </c>
       <c r="O49">
-        <v>-260.99269392</v>
+        <v>-268.13398528</v>
       </c>
       <c r="P49">
-        <v>-671.1240700799999</v>
+        <v>-689.4873907200001</v>
       </c>
       <c r="Q49">
-        <v>-605.4240700799999</v>
+        <v>-623.7873907200001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1282916031633117</v>
+        <v>0.1298779801472215</v>
       </c>
       <c r="T49">
-        <v>1.905117855965628</v>
+        <v>1.941754737811121</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.0622732594069236</v>
+        <v>0.06097589983594601</v>
       </c>
       <c r="W49">
-        <v>0.1882955295110897</v>
+        <v>0.188556039312942</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.22240449788187</v>
+        <v>0.2177710708426643</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1580434485467674</v>
+        <v>0.1595934485467674</v>
       </c>
       <c r="C50">
-        <v>-973.6480762168176</v>
+        <v>-1169.434623101151</v>
       </c>
       <c r="D50">
-        <v>5048.871923783182</v>
+        <v>4980.100376898848</v>
       </c>
       <c r="E50">
-        <v>6000.719999999999</v>
+        <v>6127.735</v>
       </c>
       <c r="F50">
-        <v>6096.719999999999</v>
+        <v>6223.735</v>
       </c>
       <c r="G50">
         <v>74.2</v>
@@ -5512,37 +5512,37 @@
         <v>266.6</v>
       </c>
       <c r="M50">
-        <v>1224.221376</v>
+        <v>1249.725988</v>
       </c>
       <c r="N50">
-        <v>-957.6213759999999</v>
+        <v>-983.1259879999999</v>
       </c>
       <c r="O50">
-        <v>-268.13398528</v>
+        <v>-275.27527664</v>
       </c>
       <c r="P50">
-        <v>-689.4873907199999</v>
+        <v>-707.8507113599999</v>
       </c>
       <c r="Q50">
-        <v>-623.7873907199998</v>
+        <v>-642.1507113599998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1298779801472215</v>
+        <v>0.1315265679932455</v>
       </c>
       <c r="T50">
-        <v>1.941754737811121</v>
+        <v>1.979828360121143</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.06097589983594602</v>
+        <v>0.05973149371684509</v>
       </c>
       <c r="W50">
-        <v>0.188556039312942</v>
+        <v>0.1888059160616575</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2177710708426643</v>
+        <v>0.2133267632744468</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1595934485467674</v>
+        <v>0.1611434485467674</v>
       </c>
       <c r="C51">
-        <v>-1169.434623101151</v>
+        <v>-1363.372848316351</v>
       </c>
       <c r="D51">
-        <v>4980.100376898848</v>
+        <v>4913.177151683649</v>
       </c>
       <c r="E51">
-        <v>6127.735</v>
+        <v>6254.75</v>
       </c>
       <c r="F51">
-        <v>6223.735</v>
+        <v>6350.75</v>
       </c>
       <c r="G51">
         <v>74.2</v>
@@ -5594,37 +5594,37 @@
         <v>266.6</v>
       </c>
       <c r="M51">
-        <v>1249.725988</v>
+        <v>1275.2306</v>
       </c>
       <c r="N51">
-        <v>-983.1259879999999</v>
+        <v>-1008.6306</v>
       </c>
       <c r="O51">
-        <v>-275.27527664</v>
+        <v>-282.416568</v>
       </c>
       <c r="P51">
-        <v>-707.8507113599999</v>
+        <v>-726.2140320000001</v>
       </c>
       <c r="Q51">
-        <v>-642.1507113599998</v>
+        <v>-660.514032</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1315265679932455</v>
+        <v>0.1332410993531104</v>
       </c>
       <c r="T51">
-        <v>1.979828360121143</v>
+        <v>2.019424927323565</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05973149371684509</v>
+        <v>0.05853686384250818</v>
       </c>
       <c r="W51">
-        <v>0.1888059160616575</v>
+        <v>0.1890457977404243</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2133267632744468</v>
+        <v>0.2090602280089577</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1611434485467674</v>
+        <v>0.1626934485467674</v>
       </c>
       <c r="C52">
-        <v>-1363.372848316351</v>
+        <v>-1555.536277760307</v>
       </c>
       <c r="D52">
-        <v>4913.177151683649</v>
+        <v>4848.028722239694</v>
       </c>
       <c r="E52">
-        <v>6254.75</v>
+        <v>6381.765</v>
       </c>
       <c r="F52">
-        <v>6350.75</v>
+        <v>6477.765</v>
       </c>
       <c r="G52">
         <v>74.2</v>
@@ -5676,37 +5676,37 @@
         <v>266.6</v>
       </c>
       <c r="M52">
-        <v>1275.2306</v>
+        <v>1300.735212</v>
       </c>
       <c r="N52">
-        <v>-1008.6306</v>
+        <v>-1034.135212</v>
       </c>
       <c r="O52">
-        <v>-282.416568</v>
+        <v>-289.5578593600001</v>
       </c>
       <c r="P52">
-        <v>-726.2140320000001</v>
+        <v>-744.5773526400001</v>
       </c>
       <c r="Q52">
-        <v>-660.514032</v>
+        <v>-678.87735264</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1332410993531104</v>
+        <v>0.1350256115848065</v>
       </c>
       <c r="T52">
-        <v>2.019424927323565</v>
+        <v>2.060637680942414</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05853686384250818</v>
+        <v>0.05738908219853743</v>
       </c>
       <c r="W52">
-        <v>0.1890457977404243</v>
+        <v>0.1892762722945337</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2090602280089577</v>
+        <v>0.2049610078519193</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1626934485467674</v>
+        <v>0.1642434485467674</v>
       </c>
       <c r="C53">
-        <v>-1555.536277760307</v>
+        <v>-1745.994588569553</v>
       </c>
       <c r="D53">
-        <v>4848.028722239694</v>
+        <v>4784.585411430447</v>
       </c>
       <c r="E53">
-        <v>6381.765</v>
+        <v>6508.780000000001</v>
       </c>
       <c r="F53">
-        <v>6477.765</v>
+        <v>6604.780000000001</v>
       </c>
       <c r="G53">
         <v>74.2</v>
@@ -5758,37 +5758,37 @@
         <v>266.6</v>
       </c>
       <c r="M53">
-        <v>1300.735212</v>
+        <v>1326.239824</v>
       </c>
       <c r="N53">
-        <v>-1034.135212</v>
+        <v>-1059.639824</v>
       </c>
       <c r="O53">
-        <v>-289.5578593600001</v>
+        <v>-296.6991507200001</v>
       </c>
       <c r="P53">
-        <v>-744.5773526400001</v>
+        <v>-762.9406732800003</v>
       </c>
       <c r="Q53">
-        <v>-678.87735264</v>
+        <v>-697.2406732800002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1350256115848065</v>
+        <v>0.1368844784928233</v>
       </c>
       <c r="T53">
-        <v>2.060637680942414</v>
+        <v>2.103567632628715</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05738908219853743</v>
+        <v>0.05628544600241171</v>
       </c>
       <c r="W53">
-        <v>0.1892762722945337</v>
+        <v>0.1894978824427157</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2049610078519193</v>
+        <v>0.2010194500086131</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1642434485467674</v>
+        <v>0.184539112200647</v>
       </c>
       <c r="C54">
-        <v>-1745.994588569553</v>
+        <v>-2572.929998130879</v>
       </c>
       <c r="D54">
-        <v>4784.585411430447</v>
+        <v>4084.665001869122</v>
       </c>
       <c r="E54">
-        <v>6508.780000000001</v>
+        <v>6635.795</v>
       </c>
       <c r="F54">
-        <v>6604.780000000001</v>
+        <v>6731.795</v>
       </c>
       <c r="G54">
         <v>74.2</v>
@@ -5840,45 +5840,45 @@
         <v>266.6</v>
       </c>
       <c r="M54">
-        <v>1326.239824</v>
+        <v>1587.357261</v>
       </c>
       <c r="N54">
-        <v>-1059.639824</v>
+        <v>-1320.757261</v>
       </c>
       <c r="O54">
-        <v>-296.6991507200001</v>
+        <v>-369.8120330800001</v>
       </c>
       <c r="P54">
-        <v>-762.9406732800003</v>
+        <v>-950.9452279200001</v>
       </c>
       <c r="Q54">
-        <v>-697.2406732800002</v>
+        <v>-885.2452279200002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1368844784928233</v>
+        <v>0.1392387517668826</v>
       </c>
       <c r="T54">
-        <v>2.103567632628715</v>
+        <v>2.157938839881815</v>
       </c>
       <c r="U54">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05628544600241171</v>
+        <v>0.04702659056914095</v>
       </c>
       <c r="W54">
-        <v>0.1894978824427157</v>
+        <v>0.2247111299437966</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.2010194500086131</v>
+        <v>0.1679521091755033</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.184539112200647</v>
+        <v>0.186439112200647</v>
       </c>
       <c r="C55">
-        <v>-2572.929998130879</v>
+        <v>-2755.127823037218</v>
       </c>
       <c r="D55">
-        <v>4084.665001869122</v>
+        <v>4029.482176962782</v>
       </c>
       <c r="E55">
-        <v>6635.795</v>
+        <v>6762.81</v>
       </c>
       <c r="F55">
-        <v>6731.795</v>
+        <v>6858.81</v>
       </c>
       <c r="G55">
         <v>74.2</v>
@@ -5922,37 +5922,37 @@
         <v>266.6</v>
       </c>
       <c r="M55">
-        <v>1587.357261</v>
+        <v>1617.307398</v>
       </c>
       <c r="N55">
-        <v>-1320.757261</v>
+        <v>-1350.707398</v>
       </c>
       <c r="O55">
-        <v>-369.8120330800001</v>
+        <v>-378.19807144</v>
       </c>
       <c r="P55">
-        <v>-950.9452279200001</v>
+        <v>-972.50932656</v>
       </c>
       <c r="Q55">
-        <v>-885.2452279200002</v>
+        <v>-906.80932656</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1392387517668826</v>
+        <v>0.1412700289792061</v>
       </c>
       <c r="T55">
-        <v>2.157938839881815</v>
+        <v>2.204850553792289</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04702659056914095</v>
+        <v>0.04615572778082352</v>
       </c>
       <c r="W55">
-        <v>0.2247111299437966</v>
+        <v>0.2249164793892818</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1679521091755033</v>
+        <v>0.1648418849315126</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.186439112200647</v>
+        <v>0.188339112200647</v>
       </c>
       <c r="C56">
-        <v>-2755.127823037218</v>
+        <v>-2935.85450973169</v>
       </c>
       <c r="D56">
-        <v>4029.482176962782</v>
+        <v>3975.770490268311</v>
       </c>
       <c r="E56">
-        <v>6762.81</v>
+        <v>6889.825000000001</v>
       </c>
       <c r="F56">
-        <v>6858.81</v>
+        <v>6985.825000000001</v>
       </c>
       <c r="G56">
         <v>74.2</v>
@@ -6004,37 +6004,37 @@
         <v>266.6</v>
       </c>
       <c r="M56">
-        <v>1617.307398</v>
+        <v>1647.257535</v>
       </c>
       <c r="N56">
-        <v>-1350.707398</v>
+        <v>-1380.657535</v>
       </c>
       <c r="O56">
-        <v>-378.19807144</v>
+        <v>-386.5841098000001</v>
       </c>
       <c r="P56">
-        <v>-972.50932656</v>
+        <v>-994.0734252000002</v>
       </c>
       <c r="Q56">
-        <v>-906.80932656</v>
+        <v>-928.3734252000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1412700289792061</v>
+        <v>0.143391585178744</v>
       </c>
       <c r="T56">
-        <v>2.204850553792289</v>
+        <v>2.253847232765451</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04615572778082352</v>
+        <v>0.0453165327302631</v>
       </c>
       <c r="W56">
-        <v>0.2249164793892818</v>
+        <v>0.225114361582204</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1648418849315126</v>
+        <v>0.1618447597509396</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.188339112200647</v>
+        <v>0.190239112200647</v>
       </c>
       <c r="C57">
-        <v>-2935.85450973169</v>
+        <v>-3115.168113734574</v>
       </c>
       <c r="D57">
-        <v>3975.770490268311</v>
+        <v>3923.471886265427</v>
       </c>
       <c r="E57">
-        <v>6889.825000000001</v>
+        <v>7016.840000000001</v>
       </c>
       <c r="F57">
-        <v>6985.825000000001</v>
+        <v>7112.840000000001</v>
       </c>
       <c r="G57">
         <v>74.2</v>
@@ -6086,37 +6086,37 @@
         <v>266.6</v>
       </c>
       <c r="M57">
-        <v>1647.257535</v>
+        <v>1677.207672</v>
       </c>
       <c r="N57">
-        <v>-1380.657535</v>
+        <v>-1410.607672</v>
       </c>
       <c r="O57">
-        <v>-386.5841098000001</v>
+        <v>-394.9701481600001</v>
       </c>
       <c r="P57">
-        <v>-994.0734252000002</v>
+        <v>-1015.63752384</v>
       </c>
       <c r="Q57">
-        <v>-928.3734252000002</v>
+        <v>-949.93752384</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.143391585178744</v>
+        <v>0.1456095757509882</v>
       </c>
       <c r="T57">
-        <v>2.253847232765451</v>
+        <v>2.30507103351012</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0453165327302631</v>
+        <v>0.04450730893150839</v>
       </c>
       <c r="W57">
-        <v>0.225114361582204</v>
+        <v>0.2253051765539503</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1618447597509396</v>
+        <v>0.1589546747553872</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.190239112200647</v>
+        <v>0.192139112200647</v>
       </c>
       <c r="C58">
-        <v>-3115.168113734574</v>
+        <v>-3293.123675501024</v>
       </c>
       <c r="D58">
-        <v>3923.471886265427</v>
+        <v>3872.531324498977</v>
       </c>
       <c r="E58">
-        <v>7016.840000000001</v>
+        <v>7143.855</v>
       </c>
       <c r="F58">
-        <v>7112.840000000001</v>
+        <v>7239.855</v>
       </c>
       <c r="G58">
         <v>74.2</v>
@@ -6168,37 +6168,37 @@
         <v>266.6</v>
       </c>
       <c r="M58">
-        <v>1677.207672</v>
+        <v>1707.157809</v>
       </c>
       <c r="N58">
-        <v>-1410.607672</v>
+        <v>-1440.557809</v>
       </c>
       <c r="O58">
-        <v>-394.9701481600001</v>
+        <v>-403.3561865200002</v>
       </c>
       <c r="P58">
-        <v>-1015.63752384</v>
+        <v>-1037.20162248</v>
       </c>
       <c r="Q58">
-        <v>-949.93752384</v>
+        <v>-971.5016224800002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1456095757509882</v>
+        <v>0.1479307286754298</v>
       </c>
       <c r="T58">
-        <v>2.30507103351012</v>
+        <v>2.358677336615008</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04450730893150839</v>
+        <v>0.04372647895025386</v>
       </c>
       <c r="W58">
-        <v>0.2253051765539503</v>
+        <v>0.2254892962635301</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1589546747553872</v>
+        <v>0.1561659962509065</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.192139112200647</v>
+        <v>0.194039112200647</v>
       </c>
       <c r="C59">
-        <v>-3293.123675501024</v>
+        <v>-3469.773413643472</v>
       </c>
       <c r="D59">
-        <v>3872.531324498977</v>
+        <v>3822.896586356529</v>
       </c>
       <c r="E59">
-        <v>7143.855</v>
+        <v>7270.870000000001</v>
       </c>
       <c r="F59">
-        <v>7239.855</v>
+        <v>7366.870000000001</v>
       </c>
       <c r="G59">
         <v>74.2</v>
@@ -6250,37 +6250,37 @@
         <v>266.6</v>
       </c>
       <c r="M59">
-        <v>1707.157809</v>
+        <v>1737.107946</v>
       </c>
       <c r="N59">
-        <v>-1440.557809</v>
+        <v>-1470.507946</v>
       </c>
       <c r="O59">
-        <v>-403.3561865200002</v>
+        <v>-411.7422248800001</v>
       </c>
       <c r="P59">
-        <v>-1037.20162248</v>
+        <v>-1058.76572112</v>
       </c>
       <c r="Q59">
-        <v>-971.5016224800002</v>
+        <v>-993.06572112</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1479307286754298</v>
+        <v>0.1503624126915115</v>
       </c>
       <c r="T59">
-        <v>2.358677336615008</v>
+        <v>2.414836320820126</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04372647895025386</v>
+        <v>0.04297257414076672</v>
       </c>
       <c r="W59">
-        <v>0.2254892962635301</v>
+        <v>0.2256670670176072</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1561659962509065</v>
+        <v>0.153473479074167</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.194039112200647</v>
+        <v>0.195939112200647</v>
       </c>
       <c r="C60">
-        <v>-3469.77341364347</v>
+        <v>-3645.166903482748</v>
       </c>
       <c r="D60">
-        <v>3822.89658635653</v>
+        <v>3774.518096517251</v>
       </c>
       <c r="E60">
-        <v>7270.87</v>
+        <v>7397.884999999999</v>
       </c>
       <c r="F60">
-        <v>7366.87</v>
+        <v>7493.884999999999</v>
       </c>
       <c r="G60">
         <v>74.2</v>
@@ -6332,37 +6332,37 @@
         <v>266.6</v>
       </c>
       <c r="M60">
-        <v>1737.107946</v>
+        <v>1767.058083</v>
       </c>
       <c r="N60">
-        <v>-1470.507946</v>
+        <v>-1500.458083</v>
       </c>
       <c r="O60">
-        <v>-411.7422248800001</v>
+        <v>-420.12826324</v>
       </c>
       <c r="P60">
-        <v>-1058.76572112</v>
+        <v>-1080.32981976</v>
       </c>
       <c r="Q60">
-        <v>-993.06572112</v>
+        <v>-1014.62981976</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1503624126915114</v>
+        <v>0.1529127154400849</v>
       </c>
       <c r="T60">
-        <v>2.414836320820125</v>
+        <v>2.473734767669397</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04297257414076673</v>
+        <v>0.04224422542651645</v>
       </c>
       <c r="W60">
-        <v>0.2256670670176072</v>
+        <v>0.2258388116444274</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1534734790741669</v>
+        <v>0.1508722336661301</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.195939112200647</v>
+        <v>0.197839112200647</v>
       </c>
       <c r="C61">
-        <v>-3645.166903482748</v>
+        <v>-3819.351242211315</v>
       </c>
       <c r="D61">
-        <v>3774.518096517251</v>
+        <v>3727.348757788685</v>
       </c>
       <c r="E61">
-        <v>7397.884999999999</v>
+        <v>7524.9</v>
       </c>
       <c r="F61">
-        <v>7493.884999999999</v>
+        <v>7620.9</v>
       </c>
       <c r="G61">
         <v>74.2</v>
@@ -6414,37 +6414,37 @@
         <v>266.6</v>
       </c>
       <c r="M61">
-        <v>1767.058083</v>
+        <v>1797.00822</v>
       </c>
       <c r="N61">
-        <v>-1500.458083</v>
+        <v>-1530.40822</v>
       </c>
       <c r="O61">
-        <v>-420.12826324</v>
+        <v>-428.5143016</v>
       </c>
       <c r="P61">
-        <v>-1080.32981976</v>
+        <v>-1101.8939184</v>
       </c>
       <c r="Q61">
-        <v>-1014.62981976</v>
+        <v>-1036.1939184</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1529127154400849</v>
+        <v>0.155590533326087</v>
       </c>
       <c r="T61">
-        <v>2.473734767669397</v>
+        <v>2.535578136861132</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04224422542651645</v>
+        <v>0.04154015500274118</v>
       </c>
       <c r="W61">
-        <v>0.2258388116444274</v>
+        <v>0.2260048314503536</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1508722336661301</v>
+        <v>0.1483576964383614</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.197839112200647</v>
+        <v>0.199739112200647</v>
       </c>
       <c r="C62">
-        <v>-3819.351242211315</v>
+        <v>-3992.371201825269</v>
       </c>
       <c r="D62">
-        <v>3727.348757788685</v>
+        <v>3681.343798174732</v>
       </c>
       <c r="E62">
-        <v>7524.9</v>
+        <v>7651.915</v>
       </c>
       <c r="F62">
-        <v>7620.9</v>
+        <v>7747.915</v>
       </c>
       <c r="G62">
         <v>74.2</v>
@@ -6496,37 +6496,37 @@
         <v>266.6</v>
       </c>
       <c r="M62">
-        <v>1797.00822</v>
+        <v>1826.958357</v>
       </c>
       <c r="N62">
-        <v>-1530.40822</v>
+        <v>-1560.358357</v>
       </c>
       <c r="O62">
-        <v>-428.5143016</v>
+        <v>-436.9003399600001</v>
       </c>
       <c r="P62">
-        <v>-1101.8939184</v>
+        <v>-1123.45801704</v>
       </c>
       <c r="Q62">
-        <v>-1036.1939184</v>
+        <v>-1057.75801704</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.155590533326087</v>
+        <v>0.1584056752062431</v>
       </c>
       <c r="T62">
-        <v>2.535578136861132</v>
+        <v>2.600592960883212</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04154015500274118</v>
+        <v>0.04085916885515525</v>
       </c>
       <c r="W62">
-        <v>0.2260048314503536</v>
+        <v>0.2261654079839544</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1483576964383614</v>
+        <v>0.1459256030541258</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.199739112200647</v>
+        <v>0.201639112200647</v>
       </c>
       <c r="C63">
-        <v>-3992.371201825269</v>
+        <v>-4164.269370869035</v>
       </c>
       <c r="D63">
-        <v>3681.343798174732</v>
+        <v>3636.460629130966</v>
       </c>
       <c r="E63">
-        <v>7651.915</v>
+        <v>7778.93</v>
       </c>
       <c r="F63">
-        <v>7747.915</v>
+        <v>7874.93</v>
       </c>
       <c r="G63">
         <v>74.2</v>
@@ -6578,37 +6578,37 @@
         <v>266.6</v>
       </c>
       <c r="M63">
-        <v>1826.958357</v>
+        <v>1856.908494</v>
       </c>
       <c r="N63">
-        <v>-1560.358357</v>
+        <v>-1590.308494</v>
       </c>
       <c r="O63">
-        <v>-436.9003399600001</v>
+        <v>-445.2863783200002</v>
       </c>
       <c r="P63">
-        <v>-1123.45801704</v>
+        <v>-1145.02211568</v>
       </c>
       <c r="Q63">
-        <v>-1057.75801704</v>
+        <v>-1079.32211568</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1584056752062431</v>
+        <v>0.1613689824485127</v>
       </c>
       <c r="T63">
-        <v>2.600592960883212</v>
+        <v>2.66902961774856</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04085916885515525</v>
+        <v>0.04020015000265275</v>
       </c>
       <c r="W63">
-        <v>0.2261654079839544</v>
+        <v>0.2263208046293745</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1459256030541258</v>
+        <v>0.1435719642951883</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.201639112200647</v>
+        <v>0.203539112200647</v>
       </c>
       <c r="C64">
-        <v>-4164.269370869035</v>
+        <v>-4335.086285935983</v>
       </c>
       <c r="D64">
-        <v>3636.460629130966</v>
+        <v>3592.658714064017</v>
       </c>
       <c r="E64">
-        <v>7778.93</v>
+        <v>7905.945</v>
       </c>
       <c r="F64">
-        <v>7874.93</v>
+        <v>8001.945</v>
       </c>
       <c r="G64">
         <v>74.2</v>
@@ -6660,37 +6660,37 @@
         <v>266.6</v>
       </c>
       <c r="M64">
-        <v>1856.908494</v>
+        <v>1886.858631</v>
       </c>
       <c r="N64">
-        <v>-1590.308494</v>
+        <v>-1620.258631</v>
       </c>
       <c r="O64">
-        <v>-445.2863783200002</v>
+        <v>-453.6724166800001</v>
       </c>
       <c r="P64">
-        <v>-1145.02211568</v>
+        <v>-1166.58621432</v>
       </c>
       <c r="Q64">
-        <v>-1079.32211568</v>
+        <v>-1100.88621432</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1613689824485127</v>
+        <v>0.1644924684606346</v>
       </c>
       <c r="T64">
-        <v>2.66902961774856</v>
+        <v>2.741165553363386</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04020015000265275</v>
+        <v>0.03956205238356302</v>
       </c>
       <c r="W64">
-        <v>0.2263208046293745</v>
+        <v>0.2264712680479558</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1435719642951883</v>
+        <v>0.1412930442270107</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.203539112200647</v>
+        <v>0.205439112200647</v>
       </c>
       <c r="C65">
-        <v>-4335.086285935983</v>
+        <v>-4504.860553778454</v>
       </c>
       <c r="D65">
-        <v>3592.658714064017</v>
+        <v>3549.899446221546</v>
       </c>
       <c r="E65">
-        <v>7905.945</v>
+        <v>8032.96</v>
       </c>
       <c r="F65">
-        <v>8001.945</v>
+        <v>8128.96</v>
       </c>
       <c r="G65">
         <v>74.2</v>
@@ -6742,37 +6742,37 @@
         <v>266.6</v>
       </c>
       <c r="M65">
-        <v>1886.858631</v>
+        <v>1916.808768</v>
       </c>
       <c r="N65">
-        <v>-1620.258631</v>
+        <v>-1650.208768</v>
       </c>
       <c r="O65">
-        <v>-453.6724166800001</v>
+        <v>-462.05845504</v>
       </c>
       <c r="P65">
-        <v>-1166.58621432</v>
+        <v>-1188.15031296</v>
       </c>
       <c r="Q65">
-        <v>-1100.88621432</v>
+        <v>-1122.45031296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1644924684606346</v>
+        <v>0.16778948147343</v>
       </c>
       <c r="T65">
-        <v>2.741165553363386</v>
+        <v>2.817309040956814</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03956205238356302</v>
+        <v>0.03894389531506985</v>
       </c>
       <c r="W65">
-        <v>0.2264712680479558</v>
+        <v>0.2266170294847066</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1412930442270107</v>
+        <v>0.1390853404109638</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.205439112200647</v>
+        <v>0.207339112200647</v>
       </c>
       <c r="C66">
-        <v>-4504.860553778454</v>
+        <v>-4673.62896480032</v>
       </c>
       <c r="D66">
-        <v>3549.899446221546</v>
+        <v>3508.14603519968</v>
       </c>
       <c r="E66">
-        <v>8032.96</v>
+        <v>8159.975</v>
       </c>
       <c r="F66">
-        <v>8128.96</v>
+        <v>8255.975</v>
       </c>
       <c r="G66">
         <v>74.2</v>
@@ -6824,37 +6824,37 @@
         <v>266.6</v>
       </c>
       <c r="M66">
-        <v>1916.808768</v>
+        <v>1946.758905</v>
       </c>
       <c r="N66">
-        <v>-1650.208768</v>
+        <v>-1680.158905</v>
       </c>
       <c r="O66">
-        <v>-462.05845504</v>
+        <v>-470.4444934000001</v>
       </c>
       <c r="P66">
-        <v>-1188.15031296</v>
+        <v>-1209.7144116</v>
       </c>
       <c r="Q66">
-        <v>-1122.45031296</v>
+        <v>-1144.0144116</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.16778948147343</v>
+        <v>0.1712748952298138</v>
       </c>
       <c r="T66">
-        <v>2.817309040956814</v>
+        <v>2.897803584984151</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03894389531506985</v>
+        <v>0.03834475846406878</v>
       </c>
       <c r="W66">
-        <v>0.2266170294847066</v>
+        <v>0.2267583059541726</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1390853404109638</v>
+        <v>0.1369455659431027</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.207339112200647</v>
+        <v>0.209239112200647</v>
       </c>
       <c r="C67">
-        <v>-4673.62896480032</v>
+        <v>-4841.42659863338</v>
       </c>
       <c r="D67">
-        <v>3508.14603519968</v>
+        <v>3467.36340136662</v>
       </c>
       <c r="E67">
-        <v>8159.975</v>
+        <v>8286.99</v>
       </c>
       <c r="F67">
-        <v>8255.975</v>
+        <v>8382.99</v>
       </c>
       <c r="G67">
         <v>74.2</v>
@@ -6906,37 +6906,37 @@
         <v>266.6</v>
       </c>
       <c r="M67">
-        <v>1946.758905</v>
+        <v>1976.709042</v>
       </c>
       <c r="N67">
-        <v>-1680.158905</v>
+        <v>-1710.109042</v>
       </c>
       <c r="O67">
-        <v>-470.4444934000001</v>
+        <v>-478.83053176</v>
       </c>
       <c r="P67">
-        <v>-1209.7144116</v>
+        <v>-1231.27851024</v>
       </c>
       <c r="Q67">
-        <v>-1144.0144116</v>
+        <v>-1165.57851024</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1712748952298138</v>
+        <v>0.1749653333248083</v>
       </c>
       <c r="T67">
-        <v>2.897803584984151</v>
+        <v>2.983033102189568</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03834475846406878</v>
+        <v>0.03776377727521925</v>
       </c>
       <c r="W67">
-        <v>0.2267583059541726</v>
+        <v>0.2268953013185033</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1369455659431027</v>
+        <v>0.134870633125783</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.209239112200647</v>
+        <v>0.211139112200647</v>
       </c>
       <c r="C68">
-        <v>-4841.42659863338</v>
+        <v>-5008.286922434332</v>
       </c>
       <c r="D68">
-        <v>3467.36340136662</v>
+        <v>3427.518077565669</v>
       </c>
       <c r="E68">
-        <v>8286.99</v>
+        <v>8414.005000000001</v>
       </c>
       <c r="F68">
-        <v>8382.99</v>
+        <v>8510.005000000001</v>
       </c>
       <c r="G68">
         <v>74.2</v>
@@ -6988,37 +6988,37 @@
         <v>266.6</v>
       </c>
       <c r="M68">
-        <v>1976.709042</v>
+        <v>2006.659179</v>
       </c>
       <c r="N68">
-        <v>-1710.109042</v>
+        <v>-1740.059179</v>
       </c>
       <c r="O68">
-        <v>-478.83053176</v>
+        <v>-487.2165701200001</v>
       </c>
       <c r="P68">
-        <v>-1231.27851024</v>
+        <v>-1252.84260888</v>
       </c>
       <c r="Q68">
-        <v>-1165.57851024</v>
+        <v>-1187.14260888</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1749653333248083</v>
+        <v>0.178879434334651</v>
       </c>
       <c r="T68">
-        <v>2.983033102189568</v>
+        <v>3.073428044680161</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03776377727521925</v>
+        <v>0.03720013880842492</v>
       </c>
       <c r="W68">
-        <v>0.2268953013185033</v>
+        <v>0.2270282072689734</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.134870633125783</v>
+        <v>0.1328576386015176</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.211139112200647</v>
+        <v>0.213039112200647</v>
       </c>
       <c r="C69">
-        <v>-5008.286922434332</v>
+        <v>-5174.241882481248</v>
       </c>
       <c r="D69">
-        <v>3427.518077565669</v>
+        <v>3388.578117518752</v>
       </c>
       <c r="E69">
-        <v>8414.005000000001</v>
+        <v>8541.02</v>
       </c>
       <c r="F69">
-        <v>8510.005000000001</v>
+        <v>8637.02</v>
       </c>
       <c r="G69">
         <v>74.2</v>
@@ -7070,37 +7070,37 @@
         <v>266.6</v>
       </c>
       <c r="M69">
-        <v>2006.659179</v>
+        <v>2036.609316</v>
       </c>
       <c r="N69">
-        <v>-1740.059179</v>
+        <v>-1770.009316</v>
       </c>
       <c r="O69">
-        <v>-487.2165701200001</v>
+        <v>-495.6026084800001</v>
       </c>
       <c r="P69">
-        <v>-1252.84260888</v>
+        <v>-1274.40670752</v>
       </c>
       <c r="Q69">
-        <v>-1187.14260888</v>
+        <v>-1208.70670752</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.178879434334651</v>
+        <v>0.1830381666576088</v>
       </c>
       <c r="T69">
-        <v>3.073428044680161</v>
+        <v>3.169472671076416</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03720013880842492</v>
+        <v>0.03665307794359515</v>
       </c>
       <c r="W69">
-        <v>0.2270282072689734</v>
+        <v>0.2271572042209003</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1328576386015176</v>
+        <v>0.1309038497985542</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.213039112200647</v>
+        <v>0.214939112200647</v>
       </c>
       <c r="C70">
-        <v>-5174.241882481248</v>
+        <v>-5339.321989596436</v>
       </c>
       <c r="D70">
-        <v>3388.578117518752</v>
+        <v>3350.513010403565</v>
       </c>
       <c r="E70">
-        <v>8541.02</v>
+        <v>8668.035</v>
       </c>
       <c r="F70">
-        <v>8637.02</v>
+        <v>8764.035</v>
       </c>
       <c r="G70">
         <v>74.2</v>
@@ -7152,37 +7152,37 @@
         <v>266.6</v>
       </c>
       <c r="M70">
-        <v>2036.609316</v>
+        <v>2066.559453</v>
       </c>
       <c r="N70">
-        <v>-1770.009316</v>
+        <v>-1799.959453</v>
       </c>
       <c r="O70">
-        <v>-495.6026084800001</v>
+        <v>-503.9886468400001</v>
       </c>
       <c r="P70">
-        <v>-1274.40670752</v>
+        <v>-1295.97080616</v>
       </c>
       <c r="Q70">
-        <v>-1208.70670752</v>
+        <v>-1230.27080616</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1830381666576088</v>
+        <v>0.1874652042917252</v>
       </c>
       <c r="T70">
-        <v>3.169472671076416</v>
+        <v>3.271713724982107</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03665307794359515</v>
+        <v>0.03612187391542711</v>
       </c>
       <c r="W70">
-        <v>0.2271572042209003</v>
+        <v>0.2272824621307423</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1309038497985542</v>
+        <v>0.1290066925550968</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.214939112200647</v>
+        <v>0.216839112200647</v>
       </c>
       <c r="C71">
-        <v>-5339.321989596436</v>
+        <v>-5503.556398875753</v>
       </c>
       <c r="D71">
-        <v>3350.513010403565</v>
+        <v>3313.293601124248</v>
       </c>
       <c r="E71">
-        <v>8668.035</v>
+        <v>8795.050000000001</v>
       </c>
       <c r="F71">
-        <v>8764.035</v>
+        <v>8891.050000000001</v>
       </c>
       <c r="G71">
         <v>74.2</v>
@@ -7234,37 +7234,37 @@
         <v>266.6</v>
       </c>
       <c r="M71">
-        <v>2066.559453</v>
+        <v>2096.50959</v>
       </c>
       <c r="N71">
-        <v>-1799.959453</v>
+        <v>-1829.90959</v>
       </c>
       <c r="O71">
-        <v>-503.9886468400001</v>
+        <v>-512.3746852000002</v>
       </c>
       <c r="P71">
-        <v>-1295.97080616</v>
+        <v>-1317.5349048</v>
       </c>
       <c r="Q71">
-        <v>-1230.27080616</v>
+        <v>-1251.8349048</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1874652042917252</v>
+        <v>0.1921873777681161</v>
       </c>
       <c r="T71">
-        <v>3.271713724982107</v>
+        <v>3.380770849148177</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03612187391542711</v>
+        <v>0.03560584714520672</v>
       </c>
       <c r="W71">
-        <v>0.2272824621307423</v>
+        <v>0.2274041412431602</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1290066925550968</v>
+        <v>0.1271637398043096</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.216839112200647</v>
+        <v>0.218739112200647</v>
       </c>
       <c r="C72">
-        <v>-5503.556398875753</v>
+        <v>-5666.972984162211</v>
       </c>
       <c r="D72">
-        <v>3313.293601124248</v>
+        <v>3276.89201583779</v>
       </c>
       <c r="E72">
-        <v>8795.050000000001</v>
+        <v>8922.065000000001</v>
       </c>
       <c r="F72">
-        <v>8891.050000000001</v>
+        <v>9018.065000000001</v>
       </c>
       <c r="G72">
         <v>74.2</v>
@@ -7316,37 +7316,37 @@
         <v>266.6</v>
       </c>
       <c r="M72">
-        <v>2096.50959</v>
+        <v>2126.459727</v>
       </c>
       <c r="N72">
-        <v>-1829.90959</v>
+        <v>-1859.859727</v>
       </c>
       <c r="O72">
-        <v>-512.3746852000002</v>
+        <v>-520.7607235600002</v>
       </c>
       <c r="P72">
-        <v>-1317.5349048</v>
+        <v>-1339.09900344</v>
       </c>
       <c r="Q72">
-        <v>-1251.8349048</v>
+        <v>-1273.39900344</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1921873777681161</v>
+        <v>0.1972352183808098</v>
       </c>
       <c r="T72">
-        <v>3.380770849148177</v>
+        <v>3.497349154291218</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03560584714520672</v>
+        <v>0.03510435634034464</v>
       </c>
       <c r="W72">
-        <v>0.2274041412431602</v>
+        <v>0.2275223927749468</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1271637398043096</v>
+        <v>0.1253727012155166</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.218739112200647</v>
+        <v>0.220639112200647</v>
       </c>
       <c r="C73">
-        <v>-5666.972984162207</v>
+        <v>-5829.598407663711</v>
       </c>
       <c r="D73">
-        <v>3276.892015837791</v>
+        <v>3241.281592336289</v>
       </c>
       <c r="E73">
-        <v>8922.064999999999</v>
+        <v>9049.08</v>
       </c>
       <c r="F73">
-        <v>9018.064999999999</v>
+        <v>9145.08</v>
       </c>
       <c r="G73">
         <v>74.2</v>
@@ -7398,37 +7398,37 @@
         <v>266.6</v>
       </c>
       <c r="M73">
-        <v>2126.459727</v>
+        <v>2156.409864</v>
       </c>
       <c r="N73">
-        <v>-1859.859727</v>
+        <v>-1889.809864</v>
       </c>
       <c r="O73">
-        <v>-520.7607235600001</v>
+        <v>-529.1467619200001</v>
       </c>
       <c r="P73">
-        <v>-1339.09900344</v>
+        <v>-1360.66310208</v>
       </c>
       <c r="Q73">
-        <v>-1273.39900344</v>
+        <v>-1294.96310208</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1972352183808097</v>
+        <v>0.2026436190372672</v>
       </c>
       <c r="T73">
-        <v>3.497349154291217</v>
+        <v>3.622254481230188</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03510435634034465</v>
+        <v>0.03461679583561764</v>
       </c>
       <c r="W73">
-        <v>0.2275223927749467</v>
+        <v>0.2276373595419614</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1253727012155166</v>
+        <v>0.1236314136986344</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.220639112200647</v>
+        <v>0.222539112200647</v>
       </c>
       <c r="C74">
-        <v>-5829.598407663711</v>
+        <v>-5991.458185080311</v>
       </c>
       <c r="D74">
-        <v>3241.281592336289</v>
+        <v>3206.436814919689</v>
       </c>
       <c r="E74">
-        <v>9049.08</v>
+        <v>9176.094999999999</v>
       </c>
       <c r="F74">
-        <v>9145.08</v>
+        <v>9272.094999999999</v>
       </c>
       <c r="G74">
         <v>74.2</v>
@@ -7480,37 +7480,37 @@
         <v>266.6</v>
       </c>
       <c r="M74">
-        <v>2156.409864</v>
+        <v>2186.360001</v>
       </c>
       <c r="N74">
-        <v>-1889.809864</v>
+        <v>-1919.760001</v>
       </c>
       <c r="O74">
-        <v>-529.1467619200001</v>
+        <v>-537.5328002800001</v>
       </c>
       <c r="P74">
-        <v>-1360.66310208</v>
+        <v>-1382.22720072</v>
       </c>
       <c r="Q74">
-        <v>-1294.96310208</v>
+        <v>-1316.52720072</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2026436190372672</v>
+        <v>0.2084526419645734</v>
       </c>
       <c r="T74">
-        <v>3.622254481230188</v>
+        <v>3.756412054609084</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03461679583561764</v>
+        <v>0.03414259315293795</v>
       </c>
       <c r="W74">
-        <v>0.2276373595419614</v>
+        <v>0.2277491765345372</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1236314136986344</v>
+        <v>0.121937832689064</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.222539112200647</v>
+        <v>0.224439112200647</v>
       </c>
       <c r="C75">
-        <v>-5991.458185080311</v>
+        <v>-6152.576746575314</v>
       </c>
       <c r="D75">
-        <v>3206.436814919689</v>
+        <v>3172.333253424687</v>
       </c>
       <c r="E75">
-        <v>9176.094999999999</v>
+        <v>9303.110000000001</v>
       </c>
       <c r="F75">
-        <v>9272.094999999999</v>
+        <v>9399.110000000001</v>
       </c>
       <c r="G75">
         <v>74.2</v>
@@ -7562,37 +7562,37 @@
         <v>266.6</v>
       </c>
       <c r="M75">
-        <v>2186.360001</v>
+        <v>2216.310138</v>
       </c>
       <c r="N75">
-        <v>-1919.760001</v>
+        <v>-1949.710138</v>
       </c>
       <c r="O75">
-        <v>-537.5328002800001</v>
+        <v>-545.9188386400001</v>
       </c>
       <c r="P75">
-        <v>-1382.22720072</v>
+        <v>-1403.79129936</v>
       </c>
       <c r="Q75">
-        <v>-1316.52720072</v>
+        <v>-1338.09129936</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2084526419645734</v>
+        <v>0.2147085128093646</v>
       </c>
       <c r="T75">
-        <v>3.756412054609084</v>
+        <v>3.900889441324818</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03414259315293795</v>
+        <v>0.03368120675897933</v>
       </c>
       <c r="W75">
-        <v>0.2277491765345372</v>
+        <v>0.2278579714462327</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.121937832689064</v>
+        <v>0.1202900241392119</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.224439112200647</v>
+        <v>0.226339112200647</v>
       </c>
       <c r="C76">
-        <v>-6152.576746575314</v>
+        <v>-6312.977493896416</v>
       </c>
       <c r="D76">
-        <v>3172.333253424687</v>
+        <v>3138.947506103584</v>
       </c>
       <c r="E76">
-        <v>9303.110000000001</v>
+        <v>9430.125</v>
       </c>
       <c r="F76">
-        <v>9399.110000000001</v>
+        <v>9526.125</v>
       </c>
       <c r="G76">
         <v>74.2</v>
@@ -7644,37 +7644,37 @@
         <v>266.6</v>
       </c>
       <c r="M76">
-        <v>2216.310138</v>
+        <v>2246.260275</v>
       </c>
       <c r="N76">
-        <v>-1949.710138</v>
+        <v>-1979.660275</v>
       </c>
       <c r="O76">
-        <v>-545.9188386400001</v>
+        <v>-554.3048770000001</v>
       </c>
       <c r="P76">
-        <v>-1403.79129936</v>
+        <v>-1425.355398</v>
       </c>
       <c r="Q76">
-        <v>-1338.09129936</v>
+        <v>-1359.655398</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2147085128093646</v>
+        <v>0.2214648533217393</v>
       </c>
       <c r="T76">
-        <v>3.900889441324818</v>
+        <v>4.056925018977812</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03368120675897933</v>
+        <v>0.03323212400219294</v>
       </c>
       <c r="W76">
-        <v>0.2278579714462327</v>
+        <v>0.2279638651602829</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1202900241392119</v>
+        <v>0.118686157150689</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.226339112200647</v>
+        <v>0.228239112200647</v>
       </c>
       <c r="C77">
-        <v>-6312.977493896416</v>
+        <v>-6472.682853927534</v>
       </c>
       <c r="D77">
-        <v>3138.947506103584</v>
+        <v>3106.257146072465</v>
       </c>
       <c r="E77">
-        <v>9430.125</v>
+        <v>9557.139999999999</v>
       </c>
       <c r="F77">
-        <v>9526.125</v>
+        <v>9653.139999999999</v>
       </c>
       <c r="G77">
         <v>74.2</v>
@@ -7726,37 +7726,37 @@
         <v>266.6</v>
       </c>
       <c r="M77">
-        <v>2246.260275</v>
+        <v>2276.210412</v>
       </c>
       <c r="N77">
-        <v>-1979.660275</v>
+        <v>-2009.610412</v>
       </c>
       <c r="O77">
-        <v>-554.3048770000001</v>
+        <v>-562.6909153600001</v>
       </c>
       <c r="P77">
-        <v>-1425.355398</v>
+        <v>-1446.91949664</v>
       </c>
       <c r="Q77">
-        <v>-1359.655398</v>
+        <v>-1381.21949664</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2214648533217393</v>
+        <v>0.2287842222101451</v>
       </c>
       <c r="T77">
-        <v>4.056925018977812</v>
+        <v>4.225963561435221</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03323212400219294</v>
+        <v>0.0327948592126904</v>
       </c>
       <c r="W77">
-        <v>0.2279638651602829</v>
+        <v>0.2280669721976476</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.118686157150689</v>
+        <v>0.11712449718818</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.228239112200647</v>
+        <v>0.230139112200647</v>
       </c>
       <c r="C78">
-        <v>-6472.682853927534</v>
+        <v>-6631.714328928856</v>
       </c>
       <c r="D78">
-        <v>3106.257146072465</v>
+        <v>3074.240671071144</v>
       </c>
       <c r="E78">
-        <v>9557.139999999999</v>
+        <v>9684.155000000001</v>
       </c>
       <c r="F78">
-        <v>9653.139999999999</v>
+        <v>9780.155000000001</v>
       </c>
       <c r="G78">
         <v>74.2</v>
@@ -7808,37 +7808,37 @@
         <v>266.6</v>
       </c>
       <c r="M78">
-        <v>2276.210412</v>
+        <v>2306.160549</v>
       </c>
       <c r="N78">
-        <v>-2009.610412</v>
+        <v>-2039.560549</v>
       </c>
       <c r="O78">
-        <v>-562.6909153600001</v>
+        <v>-571.0769537200001</v>
       </c>
       <c r="P78">
-        <v>-1446.91949664</v>
+        <v>-1468.48359528</v>
       </c>
       <c r="Q78">
-        <v>-1381.21949664</v>
+        <v>-1402.78359528</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2287842222101451</v>
+        <v>0.2367400579584122</v>
       </c>
       <c r="T78">
-        <v>4.225963561435221</v>
+        <v>4.409701107584578</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0327948592126904</v>
+        <v>0.03236895195018793</v>
       </c>
       <c r="W78">
-        <v>0.2280669721976476</v>
+        <v>0.2281674011301457</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.11712449718818</v>
+        <v>0.1156033998220997</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.230139112200647</v>
+        <v>0.232039112200647</v>
       </c>
       <c r="C79">
-        <v>-6631.714328928856</v>
+        <v>-6790.092543701605</v>
       </c>
       <c r="D79">
-        <v>3074.240671071144</v>
+        <v>3042.877456298395</v>
       </c>
       <c r="E79">
-        <v>9684.155000000001</v>
+        <v>9811.17</v>
       </c>
       <c r="F79">
-        <v>9780.155000000001</v>
+        <v>9907.17</v>
       </c>
       <c r="G79">
         <v>74.2</v>
@@ -7890,37 +7890,37 @@
         <v>266.6</v>
       </c>
       <c r="M79">
-        <v>2306.160549</v>
+        <v>2336.110686</v>
       </c>
       <c r="N79">
-        <v>-2039.560549</v>
+        <v>-2069.510686</v>
       </c>
       <c r="O79">
-        <v>-571.0769537200001</v>
+        <v>-579.46299208</v>
       </c>
       <c r="P79">
-        <v>-1468.48359528</v>
+        <v>-1490.04769392</v>
       </c>
       <c r="Q79">
-        <v>-1402.78359528</v>
+        <v>-1424.34769392</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2367400579584122</v>
+        <v>0.2454191515019764</v>
       </c>
       <c r="T79">
-        <v>4.409701107584578</v>
+        <v>4.610142067020241</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03236895195018793</v>
+        <v>0.03195396538672398</v>
       </c>
       <c r="W79">
-        <v>0.2281674011301457</v>
+        <v>0.2282652549618105</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1156033998220997</v>
+        <v>0.1141213049525855</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.232039112200647</v>
+        <v>0.233939112200647</v>
       </c>
       <c r="C80">
-        <v>-6790.092543701605</v>
+        <v>-6947.837289894951</v>
       </c>
       <c r="D80">
-        <v>3042.877456298395</v>
+        <v>3012.14771010505</v>
       </c>
       <c r="E80">
-        <v>9811.17</v>
+        <v>9938.185000000001</v>
       </c>
       <c r="F80">
-        <v>9907.17</v>
+        <v>10034.185</v>
       </c>
       <c r="G80">
         <v>74.2</v>
@@ -7972,37 +7972,37 @@
         <v>266.6</v>
       </c>
       <c r="M80">
-        <v>2336.110686</v>
+        <v>2366.060823</v>
       </c>
       <c r="N80">
-        <v>-2069.510686</v>
+        <v>-2099.460823</v>
       </c>
       <c r="O80">
-        <v>-579.46299208</v>
+        <v>-587.8490304400002</v>
       </c>
       <c r="P80">
-        <v>-1490.04769392</v>
+        <v>-1511.61179256</v>
       </c>
       <c r="Q80">
-        <v>-1424.34769392</v>
+        <v>-1445.91179256</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2454191515019764</v>
+        <v>0.2549248253830229</v>
       </c>
       <c r="T80">
-        <v>4.610142067020241</v>
+        <v>4.829672641640252</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03195396538672398</v>
+        <v>0.03154948481220848</v>
       </c>
       <c r="W80">
-        <v>0.2282652549618105</v>
+        <v>0.2283606314812813</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1141213049525855</v>
+        <v>0.1126767314721731</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.233939112200647</v>
+        <v>0.235839112200647</v>
       </c>
       <c r="C81">
-        <v>-6947.837289894951</v>
+        <v>-7104.967567655021</v>
       </c>
       <c r="D81">
-        <v>3012.14771010505</v>
+        <v>2982.03243234498</v>
       </c>
       <c r="E81">
-        <v>9938.185000000001</v>
+        <v>10065.2</v>
       </c>
       <c r="F81">
-        <v>10034.185</v>
+        <v>10161.2</v>
       </c>
       <c r="G81">
         <v>74.2</v>
@@ -8054,37 +8054,37 @@
         <v>266.6</v>
       </c>
       <c r="M81">
-        <v>2366.060823</v>
+        <v>2396.01096</v>
       </c>
       <c r="N81">
-        <v>-2099.460823</v>
+        <v>-2129.41096</v>
       </c>
       <c r="O81">
-        <v>-587.8490304400002</v>
+        <v>-596.2350688000001</v>
       </c>
       <c r="P81">
-        <v>-1511.61179256</v>
+        <v>-1533.1758912</v>
       </c>
       <c r="Q81">
-        <v>-1445.91179256</v>
+        <v>-1467.4758912</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2549248253830229</v>
+        <v>0.2653810666521741</v>
       </c>
       <c r="T81">
-        <v>4.829672641640252</v>
+        <v>5.071156273722266</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03154948481220848</v>
+        <v>0.03115511625205588</v>
       </c>
       <c r="W81">
-        <v>0.2283606314812813</v>
+        <v>0.2284536235877652</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1126767314721731</v>
+        <v>0.1112682723287709</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.235839112200647</v>
+        <v>0.237739112200647</v>
       </c>
       <c r="C82">
-        <v>-7104.967567655021</v>
+        <v>-7261.501624800249</v>
       </c>
       <c r="D82">
-        <v>2982.03243234498</v>
+        <v>2952.513375199751</v>
       </c>
       <c r="E82">
-        <v>10065.2</v>
+        <v>10192.215</v>
       </c>
       <c r="F82">
-        <v>10161.2</v>
+        <v>10288.215</v>
       </c>
       <c r="G82">
         <v>74.2</v>
@@ -8136,37 +8136,37 @@
         <v>266.6</v>
       </c>
       <c r="M82">
-        <v>2396.01096</v>
+        <v>2425.961097</v>
       </c>
       <c r="N82">
-        <v>-2129.41096</v>
+        <v>-2159.361097</v>
       </c>
       <c r="O82">
-        <v>-596.2350688000001</v>
+        <v>-604.6211071600002</v>
       </c>
       <c r="P82">
-        <v>-1533.1758912</v>
+        <v>-1554.73998984</v>
       </c>
       <c r="Q82">
-        <v>-1467.4758912</v>
+        <v>-1489.03998984</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2653810666521741</v>
+        <v>0.2769379648970254</v>
       </c>
       <c r="T82">
-        <v>5.071156273722266</v>
+        <v>5.338059235497123</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03115511625205588</v>
+        <v>0.03077048518721568</v>
       </c>
       <c r="W82">
-        <v>0.2284536235877652</v>
+        <v>0.2285443195928545</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1112682723287709</v>
+        <v>0.1098945899543416</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.237739112200647</v>
+        <v>0.239639112200647</v>
       </c>
       <c r="C83">
-        <v>-7261.501624800249</v>
+        <v>-7417.456993692742</v>
       </c>
       <c r="D83">
-        <v>2952.513375199751</v>
+        <v>2923.57300630726</v>
       </c>
       <c r="E83">
-        <v>10192.215</v>
+        <v>10319.23</v>
       </c>
       <c r="F83">
-        <v>10288.215</v>
+        <v>10415.23</v>
       </c>
       <c r="G83">
         <v>74.2</v>
@@ -8218,37 +8218,37 @@
         <v>266.6</v>
       </c>
       <c r="M83">
-        <v>2425.961097</v>
+        <v>2455.911234000001</v>
       </c>
       <c r="N83">
-        <v>-2159.361097</v>
+        <v>-2189.311234000001</v>
       </c>
       <c r="O83">
-        <v>-604.6211071600002</v>
+        <v>-613.0071455200002</v>
       </c>
       <c r="P83">
-        <v>-1554.73998984</v>
+        <v>-1576.30408848</v>
       </c>
       <c r="Q83">
-        <v>-1489.03998984</v>
+        <v>-1510.60408848</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2769379648970254</v>
+        <v>0.2897789629468601</v>
       </c>
       <c r="T83">
-        <v>5.338059235497123</v>
+        <v>5.634618081913629</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03077048518721568</v>
+        <v>0.03039523536785939</v>
       </c>
       <c r="W83">
-        <v>0.2285443195928545</v>
+        <v>0.2286328035002588</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1098945899543416</v>
+        <v>0.1085544120280691</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.239639112200647</v>
+        <v>0.241539112200647</v>
       </c>
       <c r="C84">
-        <v>-7417.456993692742</v>
+        <v>-7572.850525962212</v>
       </c>
       <c r="D84">
-        <v>2923.57300630726</v>
+        <v>2895.194474037789</v>
       </c>
       <c r="E84">
-        <v>10319.23</v>
+        <v>10446.245</v>
       </c>
       <c r="F84">
-        <v>10415.23</v>
+        <v>10542.245</v>
       </c>
       <c r="G84">
         <v>74.2</v>
@@ -8300,37 +8300,37 @@
         <v>266.6</v>
       </c>
       <c r="M84">
-        <v>2455.911234000001</v>
+        <v>2485.861371</v>
       </c>
       <c r="N84">
-        <v>-2189.311234000001</v>
+        <v>-2219.261371000001</v>
       </c>
       <c r="O84">
-        <v>-613.0071455200002</v>
+        <v>-621.3931838800002</v>
       </c>
       <c r="P84">
-        <v>-1576.30408848</v>
+        <v>-1597.86818712</v>
       </c>
       <c r="Q84">
-        <v>-1510.60408848</v>
+        <v>-1532.16818712</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2897789629468601</v>
+        <v>0.3041306666496166</v>
       </c>
       <c r="T84">
-        <v>5.634618081913629</v>
+        <v>5.966066204379137</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03039523536785939</v>
+        <v>0.03002902771282494</v>
       </c>
       <c r="W84">
-        <v>0.2286328035002588</v>
+        <v>0.2287191552653159</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1085544120280691</v>
+        <v>0.1072465275458033</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.241539112200647</v>
+        <v>0.243439112200647</v>
       </c>
       <c r="C85">
-        <v>-7572.850525962212</v>
+        <v>-7727.698425227045</v>
       </c>
       <c r="D85">
-        <v>2895.194474037789</v>
+        <v>2867.361574772955</v>
       </c>
       <c r="E85">
-        <v>10446.245</v>
+        <v>10573.26</v>
       </c>
       <c r="F85">
-        <v>10542.245</v>
+        <v>10669.26</v>
       </c>
       <c r="G85">
         <v>74.2</v>
@@ -8382,37 +8382,37 @@
         <v>266.6</v>
       </c>
       <c r="M85">
-        <v>2485.861371</v>
+        <v>2515.811508</v>
       </c>
       <c r="N85">
-        <v>-2219.261371000001</v>
+        <v>-2249.211508</v>
       </c>
       <c r="O85">
-        <v>-621.3931838800002</v>
+        <v>-629.7792222400002</v>
       </c>
       <c r="P85">
-        <v>-1597.86818712</v>
+        <v>-1619.43228576</v>
       </c>
       <c r="Q85">
-        <v>-1532.16818712</v>
+        <v>-1553.73228576</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3041306666496166</v>
+        <v>0.3202763333152178</v>
       </c>
       <c r="T85">
-        <v>5.966066204379137</v>
+        <v>6.338945342152835</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03002902771282494</v>
+        <v>0.02967153928767226</v>
       </c>
       <c r="W85">
-        <v>0.2287191552653159</v>
+        <v>0.2288034510359669</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1072465275458033</v>
+        <v>0.1059697831702581</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.243439112200647</v>
+        <v>0.245339112200647</v>
       </c>
       <c r="C86">
-        <v>-7727.698425227045</v>
+        <v>-7882.016277945917</v>
       </c>
       <c r="D86">
-        <v>2867.361574772955</v>
+        <v>2840.058722054083</v>
       </c>
       <c r="E86">
-        <v>10573.26</v>
+        <v>10700.275</v>
       </c>
       <c r="F86">
-        <v>10669.26</v>
+        <v>10796.275</v>
       </c>
       <c r="G86">
         <v>74.2</v>
@@ -8464,37 +8464,37 @@
         <v>266.6</v>
       </c>
       <c r="M86">
-        <v>2515.811508</v>
+        <v>2545.761645</v>
       </c>
       <c r="N86">
-        <v>-2249.211508</v>
+        <v>-2279.161645</v>
       </c>
       <c r="O86">
-        <v>-629.7792222400002</v>
+        <v>-638.1652606000001</v>
       </c>
       <c r="P86">
-        <v>-1619.43228576</v>
+        <v>-1640.9963844</v>
       </c>
       <c r="Q86">
-        <v>-1553.73228576</v>
+        <v>-1575.2963844</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3202763333152175</v>
+        <v>0.338574755536232</v>
       </c>
       <c r="T86">
-        <v>6.33894534215283</v>
+        <v>6.761541698296352</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02967153928767226</v>
+        <v>0.02932246235487612</v>
       </c>
       <c r="W86">
-        <v>0.2288034510359669</v>
+        <v>0.2288857633767202</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1059697831702581</v>
+        <v>0.1047230798388432</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.245339112200647</v>
+        <v>0.247239112200647</v>
       </c>
       <c r="C87">
-        <v>-7882.016277945917</v>
+        <v>-8035.819082523448</v>
       </c>
       <c r="D87">
-        <v>2840.058722054083</v>
+        <v>2813.270917476551</v>
       </c>
       <c r="E87">
-        <v>10700.275</v>
+        <v>10827.29</v>
       </c>
       <c r="F87">
-        <v>10796.275</v>
+        <v>10923.29</v>
       </c>
       <c r="G87">
         <v>74.2</v>
@@ -8546,37 +8546,37 @@
         <v>266.6</v>
       </c>
       <c r="M87">
-        <v>2545.761645</v>
+        <v>2575.711782</v>
       </c>
       <c r="N87">
-        <v>-2279.161645</v>
+        <v>-2309.111782</v>
       </c>
       <c r="O87">
-        <v>-638.1652606000001</v>
+        <v>-646.5512989600001</v>
       </c>
       <c r="P87">
-        <v>-1640.9963844</v>
+        <v>-1662.56048304</v>
       </c>
       <c r="Q87">
-        <v>-1575.2963844</v>
+        <v>-1596.86048304</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.338574755536232</v>
+        <v>0.3594872380745344</v>
       </c>
       <c r="T87">
-        <v>6.761541698296352</v>
+        <v>7.244508962460378</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02932246235487612</v>
+        <v>0.02898150349028454</v>
       </c>
       <c r="W87">
-        <v>0.2288857633767202</v>
+        <v>0.2289661614769909</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1047230798388432</v>
+        <v>0.103505369608159</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.247239112200647</v>
+        <v>0.249139112200647</v>
       </c>
       <c r="C88">
-        <v>-8035.819082523448</v>
+        <v>-8189.121276784094</v>
       </c>
       <c r="D88">
-        <v>2813.270917476551</v>
+        <v>2786.983723215906</v>
       </c>
       <c r="E88">
-        <v>10827.29</v>
+        <v>10954.305</v>
       </c>
       <c r="F88">
-        <v>10923.29</v>
+        <v>11050.305</v>
       </c>
       <c r="G88">
         <v>74.2</v>
@@ -8628,37 +8628,37 @@
         <v>266.6</v>
       </c>
       <c r="M88">
-        <v>2575.711782</v>
+        <v>2605.661919</v>
       </c>
       <c r="N88">
-        <v>-2309.111782</v>
+        <v>-2339.061919</v>
       </c>
       <c r="O88">
-        <v>-646.5512989600001</v>
+        <v>-654.9373373200001</v>
       </c>
       <c r="P88">
-        <v>-1662.56048304</v>
+        <v>-1684.12458168</v>
       </c>
       <c r="Q88">
-        <v>-1596.86048304</v>
+        <v>-1618.42458168</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3594872380745344</v>
+        <v>0.3836170256187292</v>
       </c>
       <c r="T88">
-        <v>7.244508962460378</v>
+        <v>7.801778882649637</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02898150349028454</v>
+        <v>0.02864838276051115</v>
       </c>
       <c r="W88">
-        <v>0.2289661614769909</v>
+        <v>0.2290447113450715</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.103505369608159</v>
+        <v>0.1023156527161112</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.249139112200647</v>
+        <v>0.251039112200647</v>
       </c>
       <c r="C89">
-        <v>-8189.121276784094</v>
+        <v>-8341.936763919965</v>
       </c>
       <c r="D89">
-        <v>2786.983723215906</v>
+        <v>2761.183236080035</v>
       </c>
       <c r="E89">
-        <v>10954.305</v>
+        <v>11081.32</v>
       </c>
       <c r="F89">
-        <v>11050.305</v>
+        <v>11177.32</v>
       </c>
       <c r="G89">
         <v>74.2</v>
@@ -8710,37 +8710,37 @@
         <v>266.6</v>
       </c>
       <c r="M89">
-        <v>2605.661919</v>
+        <v>2635.612056</v>
       </c>
       <c r="N89">
-        <v>-2339.061919</v>
+        <v>-2369.012056</v>
       </c>
       <c r="O89">
-        <v>-654.9373373200001</v>
+        <v>-663.32337568</v>
       </c>
       <c r="P89">
-        <v>-1684.12458168</v>
+        <v>-1705.68868032</v>
       </c>
       <c r="Q89">
-        <v>-1618.42458168</v>
+        <v>-1639.98868032</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3836170256187292</v>
+        <v>0.4117684444202901</v>
       </c>
       <c r="T89">
-        <v>7.801778882649637</v>
+        <v>8.45192712287044</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02864838276051115</v>
+        <v>0.02832283295641444</v>
       </c>
       <c r="W89">
-        <v>0.2290447113450715</v>
+        <v>0.2291214759888775</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1023156527161112</v>
+        <v>0.1011529748443373</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.251039112200647</v>
+        <v>0.252939112200647</v>
       </c>
       <c r="C90">
-        <v>-8341.936763919965</v>
+        <v>-8494.278937010629</v>
       </c>
       <c r="D90">
-        <v>2761.183236080035</v>
+        <v>2735.856062989372</v>
       </c>
       <c r="E90">
-        <v>11081.32</v>
+        <v>11208.335</v>
       </c>
       <c r="F90">
-        <v>11177.32</v>
+        <v>11304.335</v>
       </c>
       <c r="G90">
         <v>74.2</v>
@@ -8792,37 +8792,37 @@
         <v>266.6</v>
       </c>
       <c r="M90">
-        <v>2635.612056</v>
+        <v>2665.562193</v>
       </c>
       <c r="N90">
-        <v>-2369.012056</v>
+        <v>-2398.962193</v>
       </c>
       <c r="O90">
-        <v>-663.32337568</v>
+        <v>-671.7094140400002</v>
       </c>
       <c r="P90">
-        <v>-1705.68868032</v>
+        <v>-1727.25277896</v>
       </c>
       <c r="Q90">
-        <v>-1639.98868032</v>
+        <v>-1661.55277896</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4117684444202901</v>
+        <v>0.4450383030039528</v>
       </c>
       <c r="T90">
-        <v>8.45192712287044</v>
+        <v>9.220284134040481</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02832283295641444</v>
+        <v>0.02800459887825248</v>
       </c>
       <c r="W90">
-        <v>0.2291214759888775</v>
+        <v>0.2291965155845081</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1011529748443373</v>
+        <v>0.1000164245651873</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.252939112200647</v>
+        <v>0.254839112200647</v>
       </c>
       <c r="C91">
-        <v>-8494.278937010629</v>
+        <v>-8646.1607022057</v>
       </c>
       <c r="D91">
-        <v>2735.856062989372</v>
+        <v>2710.9892977943</v>
       </c>
       <c r="E91">
-        <v>11208.335</v>
+        <v>11335.35</v>
       </c>
       <c r="F91">
-        <v>11304.335</v>
+        <v>11431.35</v>
       </c>
       <c r="G91">
         <v>74.2</v>
@@ -8874,37 +8874,37 @@
         <v>266.6</v>
       </c>
       <c r="M91">
-        <v>2665.562193</v>
+        <v>2695.51233</v>
       </c>
       <c r="N91">
-        <v>-2398.962193</v>
+        <v>-2428.91233</v>
       </c>
       <c r="O91">
-        <v>-671.7094140400002</v>
+        <v>-680.0954524000001</v>
       </c>
       <c r="P91">
-        <v>-1727.25277896</v>
+        <v>-1748.8168776</v>
       </c>
       <c r="Q91">
-        <v>-1661.55277896</v>
+        <v>-1683.1168776</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4450383030039528</v>
+        <v>0.4849621333043482</v>
       </c>
       <c r="T91">
-        <v>9.220284134040481</v>
+        <v>10.14231254744453</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02800459887825248</v>
+        <v>0.02769343666849412</v>
       </c>
       <c r="W91">
-        <v>0.2291965155845081</v>
+        <v>0.2292698876335691</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1000164245651873</v>
+        <v>0.09890513095890752</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.254839112200647</v>
+        <v>0.256739112200647</v>
       </c>
       <c r="C92">
-        <v>-8646.1607022057</v>
+        <v>-8797.594500654559</v>
       </c>
       <c r="D92">
-        <v>2710.9892977943</v>
+        <v>2686.570499345441</v>
       </c>
       <c r="E92">
-        <v>11335.35</v>
+        <v>11462.365</v>
       </c>
       <c r="F92">
-        <v>11431.35</v>
+        <v>11558.365</v>
       </c>
       <c r="G92">
         <v>74.2</v>
@@ -8956,37 +8956,37 @@
         <v>266.6</v>
       </c>
       <c r="M92">
-        <v>2695.51233</v>
+        <v>2725.462467</v>
       </c>
       <c r="N92">
-        <v>-2428.91233</v>
+        <v>-2458.862467</v>
       </c>
       <c r="O92">
-        <v>-680.0954524000001</v>
+        <v>-688.48149076</v>
       </c>
       <c r="P92">
-        <v>-1748.8168776</v>
+        <v>-1770.38097624</v>
       </c>
       <c r="Q92">
-        <v>-1683.1168776</v>
+        <v>-1704.68097624</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4849621333043482</v>
+        <v>0.5337579258937203</v>
       </c>
       <c r="T92">
-        <v>10.14231254744453</v>
+        <v>11.26923616382726</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02769343666849412</v>
+        <v>0.02738911318862056</v>
       </c>
       <c r="W92">
-        <v>0.2292698876335691</v>
+        <v>0.2293416471101233</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.09890513095890752</v>
+        <v>0.09781826138793048</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.256739112200647</v>
+        <v>0.258639112200647</v>
       </c>
       <c r="C93">
-        <v>-8797.594500654559</v>
+        <v>-8948.592329261477</v>
       </c>
       <c r="D93">
-        <v>2686.570499345441</v>
+        <v>2662.587670738524</v>
       </c>
       <c r="E93">
-        <v>11462.365</v>
+        <v>11589.38</v>
       </c>
       <c r="F93">
-        <v>11558.365</v>
+        <v>11685.38</v>
       </c>
       <c r="G93">
         <v>74.2</v>
@@ -9038,37 +9038,37 @@
         <v>266.6</v>
       </c>
       <c r="M93">
-        <v>2725.462467</v>
+        <v>2755.412604000001</v>
       </c>
       <c r="N93">
-        <v>-2458.862467</v>
+        <v>-2488.812604000001</v>
       </c>
       <c r="O93">
-        <v>-688.48149076</v>
+        <v>-696.8675291200002</v>
       </c>
       <c r="P93">
-        <v>-1770.38097624</v>
+        <v>-1791.94507488</v>
       </c>
       <c r="Q93">
-        <v>-1704.68097624</v>
+        <v>-1726.24507488</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5337579258937203</v>
+        <v>0.5947526666304355</v>
       </c>
       <c r="T93">
-        <v>11.26923616382726</v>
+        <v>12.67789068430567</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02738911318862056</v>
+        <v>0.02709140543657033</v>
       </c>
       <c r="W93">
-        <v>0.2293416471101233</v>
+        <v>0.2294118465980567</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09781826138793048</v>
+        <v>0.09675501941632259</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.258639112200647</v>
+        <v>0.260539112200647</v>
       </c>
       <c r="C94">
-        <v>-8948.592329261477</v>
+        <v>-9099.165760338889</v>
       </c>
       <c r="D94">
-        <v>2662.587670738524</v>
+        <v>2639.029239661113</v>
       </c>
       <c r="E94">
-        <v>11589.38</v>
+        <v>11716.395</v>
       </c>
       <c r="F94">
-        <v>11685.38</v>
+        <v>11812.395</v>
       </c>
       <c r="G94">
         <v>74.2</v>
@@ -9120,37 +9120,37 @@
         <v>266.6</v>
       </c>
       <c r="M94">
-        <v>2755.412604000001</v>
+        <v>2785.362741</v>
       </c>
       <c r="N94">
-        <v>-2488.812604000001</v>
+        <v>-2518.762741</v>
       </c>
       <c r="O94">
-        <v>-696.8675291200002</v>
+        <v>-705.2535674800002</v>
       </c>
       <c r="P94">
-        <v>-1791.94507488</v>
+        <v>-1813.50917352</v>
       </c>
       <c r="Q94">
-        <v>-1726.24507488</v>
+        <v>-1747.80917352</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5947526666304355</v>
+        <v>0.6731744761490691</v>
       </c>
       <c r="T94">
-        <v>12.67789068430567</v>
+        <v>14.48901792492077</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02709140543657033</v>
+        <v>0.0268001000017685</v>
       </c>
       <c r="W94">
-        <v>0.2294118465980567</v>
+        <v>0.229480536419583</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.09675501941632259</v>
+        <v>0.09571464286345888</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.260539112200647</v>
+        <v>0.262439112200647</v>
       </c>
       <c r="C95">
-        <v>-9099.165760338889</v>
+        <v>-9249.325960226484</v>
       </c>
       <c r="D95">
-        <v>2639.029239661113</v>
+        <v>2615.884039773515</v>
       </c>
       <c r="E95">
-        <v>11716.395</v>
+        <v>11843.41</v>
       </c>
       <c r="F95">
-        <v>11812.395</v>
+        <v>11939.41</v>
       </c>
       <c r="G95">
         <v>74.2</v>
@@ -9202,37 +9202,37 @@
         <v>266.6</v>
       </c>
       <c r="M95">
-        <v>2785.362741</v>
+        <v>2815.312878</v>
       </c>
       <c r="N95">
-        <v>-2518.762741</v>
+        <v>-2548.712878</v>
       </c>
       <c r="O95">
-        <v>-705.2535674800002</v>
+        <v>-713.6396058400002</v>
       </c>
       <c r="P95">
-        <v>-1813.50917352</v>
+        <v>-1835.07327216</v>
       </c>
       <c r="Q95">
-        <v>-1747.80917352</v>
+        <v>-1769.37327216</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6731744761490691</v>
+        <v>0.7777368888405808</v>
       </c>
       <c r="T95">
-        <v>14.48901792492077</v>
+        <v>16.9038542457409</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0268001000017685</v>
+        <v>0.02651499255494117</v>
       </c>
       <c r="W95">
-        <v>0.229480536419583</v>
+        <v>0.2295477647555449</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.09571464286345888</v>
+        <v>0.09469640198193274</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.262439112200647</v>
+        <v>0.264339112200647</v>
       </c>
       <c r="C96">
-        <v>-9249.325960226484</v>
+        <v>-9399.08370693906</v>
       </c>
       <c r="D96">
-        <v>2615.884039773515</v>
+        <v>2593.141293060941</v>
       </c>
       <c r="E96">
-        <v>11843.41</v>
+        <v>11970.425</v>
       </c>
       <c r="F96">
-        <v>11939.41</v>
+        <v>12066.425</v>
       </c>
       <c r="G96">
         <v>74.2</v>
@@ -9284,37 +9284,37 @@
         <v>266.6</v>
       </c>
       <c r="M96">
-        <v>2815.312878</v>
+        <v>2845.263015</v>
       </c>
       <c r="N96">
-        <v>-2548.712878</v>
+        <v>-2578.663015000001</v>
       </c>
       <c r="O96">
-        <v>-713.6396058400002</v>
+        <v>-722.0256442000002</v>
       </c>
       <c r="P96">
-        <v>-1835.07327216</v>
+        <v>-1856.6373708</v>
       </c>
       <c r="Q96">
-        <v>-1769.37327216</v>
+        <v>-1790.9373708</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7777368888405808</v>
+        <v>0.9241242666086974</v>
       </c>
       <c r="T96">
-        <v>16.9038542457409</v>
+        <v>20.28462509488909</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02651499255494117</v>
+        <v>0.02623588737015232</v>
       </c>
       <c r="W96">
-        <v>0.2295477647555449</v>
+        <v>0.2296135777581181</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.09469640198193274</v>
+        <v>0.09369959775054393</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.264339112200647</v>
+        <v>0.266239112200647</v>
       </c>
       <c r="C97">
-        <v>-9399.08370693906</v>
+        <v>-9548.449406901645</v>
       </c>
       <c r="D97">
-        <v>2593.141293060941</v>
+        <v>2570.790593098355</v>
       </c>
       <c r="E97">
-        <v>11970.425</v>
+        <v>12097.44</v>
       </c>
       <c r="F97">
-        <v>12066.425</v>
+        <v>12193.44</v>
       </c>
       <c r="G97">
         <v>74.2</v>
@@ -9366,37 +9366,37 @@
         <v>266.6</v>
       </c>
       <c r="M97">
-        <v>2845.263015</v>
+        <v>2875.213152</v>
       </c>
       <c r="N97">
-        <v>-2578.663015000001</v>
+        <v>-2608.613152</v>
       </c>
       <c r="O97">
-        <v>-722.0256442000002</v>
+        <v>-730.4116825600001</v>
       </c>
       <c r="P97">
-        <v>-1856.6373708</v>
+        <v>-1878.20146944</v>
       </c>
       <c r="Q97">
-        <v>-1790.9373708</v>
+        <v>-1812.50146944</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9241242666086974</v>
+        <v>1.143705333260872</v>
       </c>
       <c r="T97">
-        <v>20.28462509488909</v>
+        <v>25.35578136861137</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02623588737015232</v>
+        <v>0.02596259687671323</v>
       </c>
       <c r="W97">
-        <v>0.2296135777581181</v>
+        <v>0.229678019656471</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.09369959775054393</v>
+        <v>0.09272356027397577</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.266239112200647</v>
+        <v>0.268139112200647</v>
       </c>
       <c r="C98">
-        <v>-9548.449406901644</v>
+        <v>-9697.433110826662</v>
       </c>
       <c r="D98">
-        <v>2570.790593098355</v>
+        <v>2548.821889173339</v>
       </c>
       <c r="E98">
-        <v>12097.44</v>
+        <v>12224.455</v>
       </c>
       <c r="F98">
-        <v>12193.44</v>
+        <v>12320.455</v>
       </c>
       <c r="G98">
         <v>74.2</v>
@@ -9448,37 +9448,37 @@
         <v>266.6</v>
       </c>
       <c r="M98">
-        <v>2875.213152</v>
+        <v>2905.163289</v>
       </c>
       <c r="N98">
-        <v>-2608.613152</v>
+        <v>-2638.563289</v>
       </c>
       <c r="O98">
-        <v>-730.41168256</v>
+        <v>-738.7977209200001</v>
       </c>
       <c r="P98">
-        <v>-1878.20146944</v>
+        <v>-1899.76556808</v>
       </c>
       <c r="Q98">
-        <v>-1812.50146944</v>
+        <v>-1834.06556808</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.143705333260869</v>
+        <v>1.509673777681159</v>
       </c>
       <c r="T98">
-        <v>25.3557813686113</v>
+        <v>33.80770849148174</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02596259687671324</v>
+        <v>0.02569494123880897</v>
       </c>
       <c r="W98">
-        <v>0.229678019656471</v>
+        <v>0.2297411328558888</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.09272356027397577</v>
+        <v>0.09176764728146058</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.268139112200647</v>
+        <v>0.270039112200647</v>
       </c>
       <c r="C99">
-        <v>-9697.433110826662</v>
+        <v>-9846.044528783828</v>
       </c>
       <c r="D99">
-        <v>2548.821889173339</v>
+        <v>2527.225471216171</v>
       </c>
       <c r="E99">
-        <v>12224.455</v>
+        <v>12351.47</v>
       </c>
       <c r="F99">
-        <v>12320.455</v>
+        <v>12447.47</v>
       </c>
       <c r="G99">
         <v>74.2</v>
@@ -9530,37 +9530,37 @@
         <v>266.6</v>
       </c>
       <c r="M99">
-        <v>2905.163289</v>
+        <v>2935.113426</v>
       </c>
       <c r="N99">
-        <v>-2638.563289</v>
+        <v>-2668.513426</v>
       </c>
       <c r="O99">
-        <v>-738.7977209200001</v>
+        <v>-747.1837592800001</v>
       </c>
       <c r="P99">
-        <v>-1899.76556808</v>
+        <v>-1921.32966672</v>
       </c>
       <c r="Q99">
-        <v>-1834.06556808</v>
+        <v>-1855.62966672</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.509673777681159</v>
+        <v>2.241610666521738</v>
       </c>
       <c r="T99">
-        <v>33.80770849148174</v>
+        <v>50.7115627372226</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02569494123880897</v>
+        <v>0.02543274796086194</v>
       </c>
       <c r="W99">
-        <v>0.2297411328558888</v>
+        <v>0.2298029580308288</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.09176764728146058</v>
+        <v>0.09083124271736409</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.270039112200647</v>
+        <v>0.271939112200647</v>
       </c>
       <c r="C100">
-        <v>-9846.044528783828</v>
+        <v>-9994.293044510425</v>
       </c>
       <c r="D100">
-        <v>2527.225471216171</v>
+        <v>2505.991955489576</v>
       </c>
       <c r="E100">
-        <v>12351.47</v>
+        <v>12478.485</v>
       </c>
       <c r="F100">
-        <v>12447.47</v>
+        <v>12574.485</v>
       </c>
       <c r="G100">
         <v>74.2</v>
@@ -9612,37 +9612,37 @@
         <v>266.6</v>
       </c>
       <c r="M100">
-        <v>2935.113426</v>
+        <v>2965.063563</v>
       </c>
       <c r="N100">
-        <v>-2668.513426</v>
+        <v>-2698.463563</v>
       </c>
       <c r="O100">
-        <v>-747.1837592800001</v>
+        <v>-755.5697976400002</v>
       </c>
       <c r="P100">
-        <v>-1921.32966672</v>
+        <v>-1942.89376536</v>
       </c>
       <c r="Q100">
-        <v>-1855.62966672</v>
+        <v>-1877.19376536</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.241610666521738</v>
+        <v>4.437421333043477</v>
       </c>
       <c r="T100">
-        <v>50.7115627372226</v>
+        <v>101.4231254744452</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02543274796086194</v>
+        <v>0.02517585151681283</v>
       </c>
       <c r="W100">
-        <v>0.2298029580308288</v>
+        <v>0.2298635342123355</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.09083124271736409</v>
+        <v>0.0899137554171886</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.271939112200647</v>
-      </c>
-      <c r="C101">
-        <v>-9994.293044510425</v>
-      </c>
-      <c r="D101">
-        <v>2505.991955489576</v>
-      </c>
-      <c r="E101">
-        <v>12478.485</v>
-      </c>
-      <c r="F101">
-        <v>12574.485</v>
-      </c>
-      <c r="G101">
-        <v>74.2</v>
-      </c>
-      <c r="H101">
-        <v>12605.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>332.3</v>
-      </c>
-      <c r="K101">
-        <v>65.69999999999999</v>
-      </c>
-      <c r="L101">
-        <v>266.6</v>
-      </c>
-      <c r="M101">
-        <v>2965.063563</v>
-      </c>
-      <c r="N101">
-        <v>-2698.463563</v>
-      </c>
-      <c r="O101">
-        <v>-755.5697976400002</v>
-      </c>
-      <c r="P101">
-        <v>-1942.89376536</v>
-      </c>
-      <c r="Q101">
-        <v>-1877.19376536</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.437421333043477</v>
-      </c>
-      <c r="T101">
-        <v>101.4231254744452</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02517585151681283</v>
-      </c>
-      <c r="W101">
-        <v>0.2298635342123355</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.0899137554171886</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
